--- a/srok_raboty_bronirovanie_kontrol.xlsx
+++ b/srok_raboty_bronirovanie_kontrol.xlsx
@@ -8,11 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По должностям (ушли)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Медиана для графика" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Количество для графика" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Отделы по годам" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Действующие" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все записи" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Срез на дату" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Когорты найма" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Медиана для графика" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Количество для графика" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Отделы по годам" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Действующие" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все записи" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -138,6 +140,88 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Средний стаж работающих на дату, дни</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Срез на дату'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Срез на дату'!$A$2:$B$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Срез на дату'!$D$2:$D$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -282,7 +366,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -427,7 +511,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -576,12 +660,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="4320000"/>
+    <ext cx="7200000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -627,6 +711,33 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1482,124 +1593,295 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Должность</t>
-        </is>
-      </c>
-      <c r="B1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D1" t="n">
-        <v>2026</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Дата среза</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Отдел</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Работало, чел</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Средний стаж, дн</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Медиана, дн</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Стаж &lt;90 дн, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Стаж &gt;1 года, %</t>
+        </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Бронирование: Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>54</v>
+          <t>31.12.2024</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>505</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>381</v>
+      </c>
+      <c r="E2" t="n">
+        <v>378</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Бронирование: Руководитель/старший</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>67</v>
+          <t>31.12.2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>1582</v>
+        <v>19</v>
+      </c>
+      <c r="D3" t="n">
+        <v>209</v>
+      </c>
+      <c r="E3" t="n">
+        <v>176</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Бронирование: Специалист по бронированию</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>10</v>
+          <t>31.12.2024</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Оба отдела</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>422</v>
+        <v>282</v>
+      </c>
+      <c r="E4" t="n">
+        <v>267</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Контроль: Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>111</v>
+          <t>31.12.2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>128</v>
+        <v>369</v>
+      </c>
+      <c r="E5" t="n">
+        <v>273</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Контроль: Менеджер 2/2</t>
-        </is>
+          <t>31.12.2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>268</v>
+      </c>
+      <c r="E6" t="n">
+        <v>177</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Контроль: Отдел контроля поездок</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>149</v>
+          <t>31.12.2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Оба отдела</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>504</v>
+        <v>40</v>
       </c>
       <c r="D7" t="n">
-        <v>848</v>
+        <v>311</v>
+      </c>
+      <c r="E7" t="n">
+        <v>209</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Контроль: Руководитель/старший</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>114</v>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>27</v>
+      </c>
+      <c r="D8" t="n">
+        <v>287</v>
+      </c>
+      <c r="E8" t="n">
+        <v>125</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>26</v>
+      </c>
+      <c r="D9" t="n">
+        <v>370</v>
+      </c>
+      <c r="E9" t="n">
+        <v>358</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Оба отдела</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>53</v>
+      </c>
+      <c r="D10" t="n">
+        <v>328</v>
+      </c>
+      <c r="E10" t="n">
+        <v>212</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
@@ -1609,6 +1891,258 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Год найма</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Отдел</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Принято</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ещё работают</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>% остались</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Средний срок работы всех (до ухода или до сегодня), дн</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Оба отдела</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>48</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F4" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>29</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F6" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Оба отдела</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F7" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>28</v>
+      </c>
+      <c r="D8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>17</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F9" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Оба отдела</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>45</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1644,13 +2178,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>505</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -1660,13 +2194,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="4">
@@ -1676,13 +2207,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5">
@@ -1692,13 +2223,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6">
@@ -1707,14 +2238,8 @@
           <t>Контроль: Менеджер 2/2</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -1724,13 +2249,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>504</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>848</v>
       </c>
     </row>
     <row r="8">
@@ -1740,13 +2265,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1755,7 +2274,154 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Должность</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D1" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Бронирование: Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Бронирование: Руководитель/старший</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Бронирование: Специалист по бронированию</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Контроль: Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Контроль: Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Контроль: Отдел контроля поездок</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Контроль: Руководитель/старший</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1822,7 +2488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2182,7 +2848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/srok_raboty_bronirovanie_kontrol.xlsx
+++ b/srok_raboty_bronirovanie_kontrol.xlsx
@@ -258,12 +258,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Медиана для графика'!$A$2:$A$8</f>
+              <f>'Медиана для графика'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Медиана для графика'!$B$2:$B$8</f>
+              <f>'Медиана для графика'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -282,12 +282,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Медиана для графика'!$A$2:$A$8</f>
+              <f>'Медиана для графика'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Медиана для графика'!$C$2:$C$8</f>
+              <f>'Медиана для графика'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -306,12 +306,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Медиана для графика'!$A$2:$A$8</f>
+              <f>'Медиана для графика'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Медиана для графика'!$D$2:$D$8</f>
+              <f>'Медиана для графика'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -403,12 +403,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Количество для графика'!$A$2:$A$8</f>
+              <f>'Количество для графика'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Количество для графика'!$B$2:$B$8</f>
+              <f>'Количество для графика'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -427,12 +427,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Количество для графика'!$A$2:$A$8</f>
+              <f>'Количество для графика'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Количество для графика'!$C$2:$C$8</f>
+              <f>'Количество для графика'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -451,12 +451,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Количество для графика'!$A$2:$A$8</f>
+              <f>'Количество для графика'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Количество для графика'!$D$2:$D$8</f>
+              <f>'Количество для графика'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -1053,7 +1053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1117,19 +1117,19 @@
         <v>2024</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
@@ -1147,19 +1147,19 @@
         <v>2025</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>422</v>
+        <v>269</v>
       </c>
       <c r="F3" t="n">
-        <v>505</v>
+        <v>360</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="4">
@@ -1177,409 +1177,139 @@
         <v>2026</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Руководитель/старший</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2024</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Руководитель/старший</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2025</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>1582</v>
+        <v>137</v>
       </c>
       <c r="F6" t="n">
-        <v>1582</v>
+        <v>110</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Специалист по бронированию</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>425</v>
-      </c>
-      <c r="F9" t="n">
-        <v>422</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D10" t="n">
-        <v>13</v>
-      </c>
-      <c r="E10" t="n">
-        <v>157</v>
-      </c>
-      <c r="F10" t="n">
-        <v>111</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D11" t="n">
-        <v>20</v>
-      </c>
-      <c r="E11" t="n">
-        <v>137</v>
-      </c>
-      <c r="F11" t="n">
-        <v>110</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D12" t="n">
-        <v>11</v>
-      </c>
-      <c r="E12" t="n">
-        <v>130</v>
-      </c>
-      <c r="F12" t="n">
-        <v>128</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>12</v>
-      </c>
-      <c r="F13" t="n">
-        <v>12</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" s="2" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Отдел контроля поездок</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D14" t="n">
-        <v>9</v>
-      </c>
-      <c r="E14" t="n">
-        <v>141</v>
-      </c>
-      <c r="F14" t="n">
-        <v>149</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Отдел контроля поездок</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>491</v>
-      </c>
-      <c r="F15" t="n">
-        <v>504</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Отдел контроля поездок</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>848</v>
-      </c>
-      <c r="F16" t="n">
-        <v>848</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Руководитель/старший</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>114</v>
-      </c>
-      <c r="F17" t="n">
-        <v>114</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1653,19 +1383,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>381</v>
+        <v>178</v>
       </c>
       <c r="E2" t="n">
-        <v>378</v>
+        <v>166</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1680,19 +1410,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>209</v>
+        <v>98</v>
       </c>
       <c r="E3" t="n">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1707,19 +1437,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>282</v>
+        <v>121</v>
       </c>
       <c r="E4" t="n">
-        <v>267</v>
+        <v>132</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1734,19 +1464,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>369</v>
+        <v>262</v>
       </c>
       <c r="E5" t="n">
-        <v>273</v>
+        <v>132</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.41</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="6">
@@ -1761,19 +1491,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>268</v>
+        <v>179</v>
       </c>
       <c r="E6" t="n">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="7">
@@ -1788,19 +1518,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>311</v>
+        <v>199</v>
       </c>
       <c r="E7" t="n">
-        <v>209</v>
+        <v>132</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
@@ -1815,19 +1545,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>287</v>
+        <v>206</v>
       </c>
       <c r="E8" t="n">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="9">
@@ -1842,19 +1572,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>370</v>
+        <v>294</v>
       </c>
       <c r="E9" t="n">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="10">
@@ -1869,19 +1599,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D10" t="n">
-        <v>328</v>
+        <v>250</v>
       </c>
       <c r="E10" t="n">
-        <v>212</v>
+        <v>132</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.38</v>
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -1949,16 +1679,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="F2" t="n">
-        <v>229</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3">
@@ -1971,16 +1701,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0.19</v>
       </c>
       <c r="F3" t="n">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4">
@@ -1993,16 +1723,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="F4" t="n">
-        <v>254</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5">
@@ -2015,16 +1745,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.24</v>
+        <v>0.6</v>
       </c>
       <c r="F5" t="n">
-        <v>233</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6">
@@ -2059,16 +1789,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="F7" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8">
@@ -2148,7 +1878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2178,94 +1908,39 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>505</v>
+        <v>360</v>
       </c>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Бронирование: Руководитель/старший</t>
+          <t>Контроль: Менеджер (основной)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>1582</v>
+        <v>110</v>
+      </c>
+      <c r="D3" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Бронирование: Специалист по бронированию</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C4" t="n">
-        <v>62</v>
+          <t>Контроль: Менеджер 2/2</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Контроль: Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>111</v>
-      </c>
-      <c r="C5" t="n">
-        <v>110</v>
-      </c>
-      <c r="D5" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Контроль: Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
         <v>12</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Контроль: Отдел контроля поездок</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>149</v>
-      </c>
-      <c r="C7" t="n">
-        <v>504</v>
-      </c>
-      <c r="D7" t="n">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Контроль: Руководитель/старший</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2280,7 +1955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2310,109 +1985,45 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Бронирование: Руководитель/старший</t>
+          <t>Контроль: Менеджер (основной)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Бронирование: Специалист по бронированию</t>
+          <t>Контроль: Менеджер 2/2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Контроль: Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D5" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Контроль: Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Контроль: Отдел контроля поездок</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Контроль: Руководитель/старший</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2457,13 +2068,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>176</v>
+        <v>360</v>
       </c>
       <c r="D2" t="n">
-        <v>165</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -2473,13 +2084,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>131</v>
+        <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D3" t="n">
-        <v>111</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2494,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2561,13 +2172,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1032</v>
+        <v>850</v>
       </c>
     </row>
     <row r="4">
@@ -2582,13 +2193,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>850</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5">
@@ -2603,13 +2214,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>392</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6">
@@ -2620,59 +2231,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2026</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>209</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Вечерний менеджер</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2026</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>472</v>
+        <v>763</v>
       </c>
     </row>
     <row r="9">
@@ -2683,17 +2294,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>19</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10">
@@ -2704,17 +2315,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Логист отдела контроля</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>828</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -2725,122 +2336,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9</v>
-      </c>
-      <c r="E13" t="n">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D15" t="n">
-        <v>8</v>
-      </c>
-      <c r="E15" t="n">
         <v>31</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Отдел контроля поездок</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>926</v>
       </c>
     </row>
   </sheetData>
@@ -2854,7 +2360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2906,12 +2412,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ксения Коваленко</t>
+          <t>Дуйшенкул кызы Эрке</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2925,27 +2431,27 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>44956</v>
+        <v>45315</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>44987</v>
+        <v>45350</v>
       </c>
       <c r="G2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Алтынай Шергазы Кызы</t>
+          <t>Морозова Кристина Александровна</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2959,27 +2465,27 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>44952</v>
+        <v>45426</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>45012</v>
+        <v>45436</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Пушкарева Лидия</t>
+          <t>Ховалыг Дан-Хаяа Шолбановна</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2993,22 +2499,22 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>45015</v>
+        <v>45488</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Дружинина Наталья</t>
+          <t>Удалова Виктория</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3027,27 +2533,27 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>45012</v>
+        <v>45481</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>45030</v>
+        <v>45497</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Нисофорова Анастасия</t>
+          <t>Акимова Анастасия Константиновна</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3061,22 +2567,22 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>45026</v>
+        <v>45474</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>45034</v>
+        <v>45526</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="H6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Константин Афирдиев</t>
+          <t>Нахтигаль Глеб Сергеевич</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3095,27 +2601,27 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>45131</v>
+        <v>45511</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>45187</v>
+        <v>45517</v>
       </c>
       <c r="G7" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Быстрова Маргарита</t>
+          <t>Коми Надежда Геннадьевна</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3129,27 +2635,27 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>45194</v>
+        <v>45488</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>45202</v>
+        <v>45560</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Беристова Алёна</t>
+          <t>Червинская Виктория</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3163,27 +2669,27 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>45145</v>
+        <v>45544</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>45215</v>
+        <v>45567</v>
       </c>
       <c r="G9" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="H9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Карвандина Татьяна</t>
+          <t>Карлин Иван</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3197,22 +2703,22 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>44951</v>
+        <v>45544</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>45169</v>
+        <v>45572</v>
       </c>
       <c r="G10" t="n">
-        <v>218</v>
+        <v>28</v>
       </c>
       <c r="H10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Королева Валерия</t>
+          <t>Егембердиев Тимур</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3231,22 +2737,22 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>45110</v>
+        <v>45575</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>45251</v>
+        <v>45583</v>
       </c>
       <c r="G11" t="n">
-        <v>141</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Задорожный Александр</t>
+          <t>Мухина Эльвира</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3256,7 +2762,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3265,32 +2771,32 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>45237</v>
+        <v>45509</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>45275</v>
+        <v>45586</v>
       </c>
       <c r="G12" t="n">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="H12" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Кислицын Даниил Дмитриевич</t>
+          <t>Козлова Мария Викторовна</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3299,22 +2805,22 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>45251</v>
+        <v>45474</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>45273</v>
+        <v>45610</v>
       </c>
       <c r="G13" t="n">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="H13" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Умуршадян Регина Александровна</t>
+          <t>Беженарь Данил</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3324,7 +2830,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3333,22 +2839,22 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>45254</v>
+        <v>45552</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>45271</v>
+        <v>45611</v>
       </c>
       <c r="G14" t="n">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="H14" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Субботина Альбина</t>
+          <t>Гафуров Ильхом Азамджонович</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3367,22 +2873,22 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>45006</v>
+        <v>45482</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>45275</v>
+        <v>45628</v>
       </c>
       <c r="G15" t="n">
-        <v>269</v>
+        <v>146</v>
       </c>
       <c r="H15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Мельникова Элина</t>
+          <t xml:space="preserve">Микрюков Олег </t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3392,7 +2898,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3401,27 +2907,27 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>45243</v>
+        <v>45495</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>45281</v>
+        <v>45652</v>
       </c>
       <c r="G16" t="n">
-        <v>38</v>
+        <v>157</v>
       </c>
       <c r="H16" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Вишнякова Ева</t>
+          <t>Петрушина Александра</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3435,13 +2941,13 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>44970</v>
+        <v>45544</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>45327</v>
+        <v>45654</v>
       </c>
       <c r="G17" t="n">
-        <v>357</v>
+        <v>110</v>
       </c>
       <c r="H17" t="n">
         <v>2024</v>
@@ -3450,12 +2956,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Коляко Виталий Олегович</t>
+          <t>Тильга Александра</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3469,22 +2975,22 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>45281</v>
+        <v>45623</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>45327</v>
+        <v>45699</v>
       </c>
       <c r="G18" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="H18" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Скачилов Максим Сергеевич</t>
+          <t>Баздылев Иван</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3494,7 +3000,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3503,27 +3009,27 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>45323</v>
+        <v>45623</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>45369</v>
+        <v>45716</v>
       </c>
       <c r="G19" t="n">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="H19" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Дуйшенкул кызы Эрке</t>
+          <t>Лепехина Диана</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3537,27 +3043,27 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>45315</v>
+        <v>45531</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>45350</v>
+        <v>45734</v>
       </c>
       <c r="G20" t="n">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="H20" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Назаров Максим Дмитриевич</t>
+          <t>Константинов Павел</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3571,22 +3077,22 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>45383</v>
+        <v>45726</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>45384</v>
+        <v>45755</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="H21" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Анисимов Иван</t>
+          <t>Гребенщикова Софья</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3605,22 +3111,22 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>44970</v>
+        <v>45650</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>45392</v>
+        <v>45789</v>
       </c>
       <c r="G22" t="n">
-        <v>422</v>
+        <v>139</v>
       </c>
       <c r="H22" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Кривошеин Артур Эдуардович</t>
+          <t>Березуцкая Светлана</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3639,22 +3145,22 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>45308</v>
+        <v>45454</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>45404</v>
+        <v>45842</v>
       </c>
       <c r="G23" t="n">
-        <v>96</v>
+        <v>388</v>
       </c>
       <c r="H23" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Таранюк Лидия</t>
+          <t>Загнитковская Арина</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3664,7 +3170,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3673,22 +3179,22 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>45261</v>
+        <v>45523</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>45418</v>
+        <v>45852</v>
       </c>
       <c r="G24" t="n">
-        <v>157</v>
+        <v>329</v>
       </c>
       <c r="H24" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Байтыков Ринат</t>
+          <t>Степанов Тимофей</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3707,27 +3213,27 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>45156</v>
+        <v>45749</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>45420</v>
+        <v>45854</v>
       </c>
       <c r="G25" t="n">
-        <v>264</v>
+        <v>105</v>
       </c>
       <c r="H25" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ивлев Фёдор Константинович</t>
+          <t>Герасименко Илья</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3741,22 +3247,22 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>45369</v>
+        <v>45810</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>45426</v>
+        <v>45854</v>
       </c>
       <c r="G26" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="H26" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Клеменкова Александра</t>
+          <t>Ткаченко Виктория</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3775,27 +3281,27 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>45399</v>
+        <v>45757</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>45400</v>
+        <v>45868</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="H27" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Морозова Кристина Александровна</t>
+          <t>Каминицкас Альгис Витальевич</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3809,22 +3315,22 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>45426</v>
+        <v>45841</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>45436</v>
+        <v>45882</v>
       </c>
       <c r="G28" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="H28" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Подлатов Михаил</t>
+          <t>Загнитковская Арина</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3834,7 +3340,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3843,22 +3349,22 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>45440</v>
+        <v>45523</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>45449</v>
+        <v>45852</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>329</v>
       </c>
       <c r="H29" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Живицкий Олег Вадимович</t>
+          <t>Кашулин Данил Сергеевич</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3868,7 +3374,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3877,22 +3383,22 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>45264</v>
+        <v>45887</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>45460</v>
+        <v>45891</v>
       </c>
       <c r="G30" t="n">
-        <v>196</v>
+        <v>4</v>
       </c>
       <c r="H30" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Колпаков Максим Станиславович</t>
+          <t>Тыщенко Анжелика Сергеевна</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3911,27 +3417,27 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>45153</v>
+        <v>45481</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>45351</v>
+        <v>45904</v>
       </c>
       <c r="G31" t="n">
-        <v>198</v>
+        <v>423</v>
       </c>
       <c r="H31" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ильтимиров Никита Сергеевич</t>
+          <t>Кирнос Наталья</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3945,22 +3451,22 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>45202</v>
+        <v>45544</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>45313</v>
+        <v>45904</v>
       </c>
       <c r="G32" t="n">
-        <v>111</v>
+        <v>360</v>
       </c>
       <c r="H32" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Малетин Андрей Сергеевич</t>
+          <t>Винтер Максим Генрихович</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3970,7 +3476,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3979,22 +3485,22 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>45308</v>
+        <v>45775</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>45457</v>
+        <v>45922</v>
       </c>
       <c r="G33" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H33" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Безденежных Владислав Альбертович</t>
+          <t xml:space="preserve">Торден Дамиан </t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4004,7 +3510,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4013,27 +3519,27 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>45426</v>
+        <v>45819</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>45476</v>
+        <v>45929</v>
       </c>
       <c r="G34" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H34" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ховалыг Дан-Хаяа Шолбановна</t>
+          <t>Винтер Максим Генрихович</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4047,22 +3553,22 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>45468</v>
+        <v>45775</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>45488</v>
+        <v>45922</v>
       </c>
       <c r="G35" t="n">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="H35" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Удалова Виктория</t>
+          <t>Бураков Григорий Радиевич</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4081,27 +3587,27 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>45481</v>
+        <v>45772</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>45497</v>
+        <v>45957</v>
       </c>
       <c r="G36" t="n">
-        <v>16</v>
+        <v>185</v>
       </c>
       <c r="H36" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Дробина Анастасия Денисовна</t>
+          <t>Парфенова Анастасия Игоревна</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4115,27 +3621,27 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>45237</v>
+        <v>45916</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>45534</v>
+        <v>45968</v>
       </c>
       <c r="G37" t="n">
-        <v>297</v>
+        <v>52</v>
       </c>
       <c r="H37" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Денк Данила Андреевич</t>
+          <t>Монгуш Анай-Хаак Андреевна</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4149,32 +3655,32 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>45251</v>
+        <v>45950</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>45534</v>
+        <v>46001</v>
       </c>
       <c r="G38" t="n">
-        <v>283</v>
+        <v>51</v>
       </c>
       <c r="H38" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Подлипаева Екатерина Андреевна</t>
+          <t>Смирнова Полина Ильинична</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4183,22 +3689,22 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>45261</v>
+        <v>45958</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>45527</v>
+        <v>46017</v>
       </c>
       <c r="G39" t="n">
-        <v>266</v>
+        <v>59</v>
       </c>
       <c r="H39" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Дьяконов Андрей Андреевич</t>
+          <t>Федоринова София Владимировна</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4208,7 +3714,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4217,32 +3723,32 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>45261</v>
+        <v>45908</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>45526</v>
+        <v>46021</v>
       </c>
       <c r="G40" t="n">
-        <v>265</v>
+        <v>113</v>
       </c>
       <c r="H40" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Нагорная Виктория Николаевна</t>
+          <t>Креймер Константин Андреевич</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Руководитель/старший</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4251,27 +3757,27 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>45460</v>
+        <v>45944</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>45527</v>
+        <v>46038</v>
       </c>
       <c r="G41" t="n">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="H41" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Акимова Анастасия Константиновна</t>
+          <t>Телков Данил Артемович</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4285,22 +3791,22 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>45474</v>
+        <v>45791</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>45526</v>
+        <v>46045</v>
       </c>
       <c r="G42" t="n">
-        <v>52</v>
+        <v>254</v>
       </c>
       <c r="H42" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Нахтигаль Глеб Сергеевич</t>
+          <t>Доржу Долума Шой-ооловна</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4319,22 +3825,22 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>45511</v>
+        <v>45880</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>45517</v>
+        <v>46059</v>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
+        <v>179</v>
       </c>
       <c r="H43" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Остапчук Олеся Дмитриевна</t>
+          <t>Лаврентьева Ульяна Ивановна</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4353,22 +3859,22 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>45176</v>
+        <v>46036</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>45539</v>
+        <v>46083</v>
       </c>
       <c r="G44" t="n">
-        <v>363</v>
+        <v>47</v>
       </c>
       <c r="H44" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Коми Надежда Геннадьевна</t>
+          <t>Рыбников Бронислав Игоревич</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4387,27 +3893,27 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>45488</v>
+        <v>46038</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>45560</v>
+        <v>46080</v>
       </c>
       <c r="G45" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="H45" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Червинская Виктория</t>
+          <t>Домрачев Иван Дмитриевич</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4421,27 +3927,27 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>45544</v>
+        <v>46091</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>45567</v>
+        <v>46097</v>
       </c>
       <c r="G46" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Карлин Иван</t>
+          <t>Хрипченко Анастасия Олеговна</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4455,22 +3961,22 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>45544</v>
+        <v>45971</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>45572</v>
+        <v>46099</v>
       </c>
       <c r="G47" t="n">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="H47" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Егембердиев Тимур</t>
+          <t xml:space="preserve">Шивлякова Мария </t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4489,22 +3995,22 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>45575</v>
+        <v>46128</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>45583</v>
+        <v>46133</v>
       </c>
       <c r="G48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H48" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Мухина Эльвира</t>
+          <t xml:space="preserve">Савкин Глеб Петрович </t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4523,22 +4029,22 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>45509</v>
+        <v>45939</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>45586</v>
+        <v>46141</v>
       </c>
       <c r="G49" t="n">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="H49" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Тимошенко Вера Васильевна</t>
+          <t>Ковалева Виктория Сергеевна</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4548,7 +4054,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Руководитель/старший</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4557,22 +4063,22 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>45482</v>
+        <v>45945</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>45596</v>
+        <v>46140</v>
       </c>
       <c r="G50" t="n">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="H50" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Азаренко Александра Юрьевна</t>
+          <t xml:space="preserve">Чернятьева Рина Витальевна </t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4582,7 +4088,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4591,22 +4097,22 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>45467</v>
+        <v>46077</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>45598</v>
+        <v>46146</v>
       </c>
       <c r="G51" t="n">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="H51" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Козлова Мария Викторовна</t>
+          <t>Карпова Валерия константиновна</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4625,27 +4131,27 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>45474</v>
+        <v>45890</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>45610</v>
+        <v>46147</v>
       </c>
       <c r="G52" t="n">
-        <v>136</v>
+        <v>257</v>
       </c>
       <c r="H52" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Беженарь Данил</t>
+          <t>Кладов Антон Павлович</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4659,22 +4165,22 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>45552</v>
+        <v>46133</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>45611</v>
+        <v>46161</v>
       </c>
       <c r="G53" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="H53" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Гафуров Ильхом Азамджонович</t>
+          <t>Резинкина Анастасия</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4693,22 +4199,22 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>45482</v>
+        <v>46162</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>45628</v>
+        <v>46183</v>
       </c>
       <c r="G54" t="n">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="H54" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Минина Алена</t>
+          <t>Самодурова Арина</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4718,7 +4224,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4727,27 +4233,27 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>45628</v>
+        <v>46164</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>45638</v>
+        <v>46188</v>
       </c>
       <c r="G55" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H55" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Микрюков Олег </t>
+          <t>Сыдыбаев Жалынбек Сыртбаевич</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4761,27 +4267,27 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>45495</v>
+        <v>46181</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>45652</v>
+        <v>46189</v>
       </c>
       <c r="G56" t="n">
-        <v>157</v>
+        <v>8</v>
       </c>
       <c r="H56" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Петрушина Александра</t>
+          <t>Мищенко Михаил Витальевич</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4795,27 +4301,27 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>45544</v>
+        <v>45966</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>45654</v>
+        <v>46220</v>
       </c>
       <c r="G57" t="n">
-        <v>110</v>
+        <v>254</v>
       </c>
       <c r="H57" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Тильга Александра</t>
+          <t>Долгополова Елена Сергеевна</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4829,22 +4335,22 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>45623</v>
+        <v>46174</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>45699</v>
+        <v>46223</v>
       </c>
       <c r="G58" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="H58" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шостенко Артём </t>
+          <t>Жигалёв Денис Евгеньевич</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4854,7 +4360,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4863,27 +4369,27 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>45671</v>
+        <v>46203</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>45705</v>
+        <v>46227</v>
       </c>
       <c r="G59" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H59" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Баздылев Иван</t>
+          <t>Кочева Анна Алексеевна</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4897,27 +4403,27 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>45623</v>
+        <v>46062</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>45716</v>
+        <v>46227</v>
       </c>
       <c r="G60" t="n">
-        <v>93</v>
+        <v>165</v>
       </c>
       <c r="H60" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Лепехина Диана</t>
+          <t>Гундарева Виктория Константиновна</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4931,22 +4437,22 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>45531</v>
+        <v>46085</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>45734</v>
+        <v>46234</v>
       </c>
       <c r="G61" t="n">
-        <v>203</v>
+        <v>149</v>
       </c>
       <c r="H61" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Константинов Павел</t>
+          <t>Сериккали Мадина</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4956,7 +4462,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4965,32 +4471,32 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>45726</v>
+        <v>46237</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>45755</v>
+        <v>46252</v>
       </c>
       <c r="G62" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H62" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Косицын Никита</t>
+          <t>Власов Тимофей Антонович</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4999,22 +4505,22 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>45726</v>
+        <v>46258</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>45762</v>
+        <v>46266</v>
       </c>
       <c r="G63" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="H63" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Нуянзина Мила Андреевна</t>
+          <t>Сазонов Сергей Викторович</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5029,26 +4535,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>45272</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>45777</v>
+        <v>45390</v>
       </c>
       <c r="G64" t="n">
-        <v>505</v>
-      </c>
-      <c r="H64" t="n">
-        <v>2025</v>
+        <v>919</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Бекреев Михаил Михайлович</t>
+          <t xml:space="preserve">Кралинова Алена Алексеевна </t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5058,31 +4558,25 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>45279</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>45782</v>
+        <v>45502</v>
       </c>
       <c r="G65" t="n">
-        <v>503</v>
-      </c>
-      <c r="H65" t="n">
-        <v>2025</v>
+        <v>807</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Федотов Александр</t>
+          <t>Русских Юлия</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5092,36 +4586,30 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>45408</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>45782</v>
+        <v>45520</v>
       </c>
       <c r="G66" t="n">
-        <v>374</v>
-      </c>
-      <c r="H66" t="n">
-        <v>2025</v>
+        <v>789</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Гребенщикова Софья</t>
+          <t>Светашова Анастасия Владимировна</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5131,26 +4619,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>45650</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>45789</v>
+        <v>45527</v>
       </c>
       <c r="G67" t="n">
-        <v>139</v>
-      </c>
-      <c r="H67" t="n">
-        <v>2025</v>
+        <v>782</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Глуховская (Мамонтова) Анна Дмитриевна</t>
+          <t>Шакирзянова Куддусия</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5160,70 +4642,58 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>45280</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>45784</v>
+        <v>45616</v>
       </c>
       <c r="G68" t="n">
-        <v>504</v>
-      </c>
-      <c r="H68" t="n">
-        <v>2025</v>
+        <v>693</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Прожерина Кристина</t>
+          <t>Краснов Сергей Витальевич</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>45735</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>45799</v>
+        <v>45775</v>
       </c>
       <c r="G69" t="n">
-        <v>64</v>
-      </c>
-      <c r="H69" t="n">
-        <v>2025</v>
+        <v>534</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Немчинов Михаил</t>
+          <t xml:space="preserve">Лемешев Филипп Игоревич </t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5233,65 +4703,53 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>45237</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>45807</v>
+        <v>45792</v>
       </c>
       <c r="G70" t="n">
-        <v>570</v>
-      </c>
-      <c r="H70" t="n">
-        <v>2025</v>
+        <v>517</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цунаев Олег </t>
+          <t>Голев Кирилл Андреевич</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>45671</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>45835</v>
+        <v>45845</v>
       </c>
       <c r="G71" t="n">
-        <v>164</v>
-      </c>
-      <c r="H71" t="n">
-        <v>2025</v>
+        <v>464</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Березуцкая Светлана</t>
+          <t>Сакирко Виктория Алексеевна</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5301,31 +4759,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>45454</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>45842</v>
+        <v>45838</v>
       </c>
       <c r="G72" t="n">
-        <v>388</v>
-      </c>
-      <c r="H72" t="n">
-        <v>2025</v>
+        <v>471</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Загнитковская Арина</t>
+          <t>Лебёдка Богдан Константинович</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5335,65 +4787,53 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>45523</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>45852</v>
+        <v>45890</v>
       </c>
       <c r="G73" t="n">
-        <v>329</v>
-      </c>
-      <c r="H73" t="n">
-        <v>2025</v>
+        <v>419</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Тимофеев Никита Сергеевич</t>
+          <t>Габазов Тимур Алиханович</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>45834</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>45847</v>
+        <v>45880</v>
       </c>
       <c r="G74" t="n">
-        <v>13</v>
-      </c>
-      <c r="H74" t="n">
-        <v>2025</v>
+        <v>429</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Степанов Тимофей</t>
+          <t>Бобров Андрей Юрьевич</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5403,31 +4843,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>45749</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>45854</v>
+        <v>45930</v>
       </c>
       <c r="G75" t="n">
-        <v>105</v>
-      </c>
-      <c r="H75" t="n">
-        <v>2025</v>
+        <v>379</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Герасименко Илья</t>
+          <t>Матющенко Ксения Евгеньевна</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5437,26 +4871,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>45810</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>45854</v>
+        <v>45930</v>
       </c>
       <c r="G76" t="n">
-        <v>44</v>
-      </c>
-      <c r="H76" t="n">
-        <v>2025</v>
+        <v>379</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ткаченко Виктория</t>
+          <t>Бахтина Виктория Александровна</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5471,60 +4899,48 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>45757</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>45868</v>
+        <v>45944</v>
       </c>
       <c r="G77" t="n">
-        <v>111</v>
-      </c>
-      <c r="H77" t="n">
-        <v>2025</v>
+        <v>365</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Бельтяева Анель</t>
+          <t>Коркунова Дарья Витальевна</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>45811</v>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>45870</v>
+        <v>45958</v>
       </c>
       <c r="G78" t="n">
-        <v>59</v>
-      </c>
-      <c r="H78" t="n">
-        <v>2025</v>
+        <v>351</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Каминицкас Альгис Витальевич</t>
+          <t>Московских Алёна Владимировна</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5539,31 +4955,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>45841</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>45882</v>
+        <v>45945</v>
       </c>
       <c r="G79" t="n">
-        <v>41</v>
-      </c>
-      <c r="H79" t="n">
-        <v>2025</v>
+        <v>364</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Немчинов Михаил</t>
+          <t>Петрова Евгения Вячеславовна</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5573,60 +4983,48 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>45237</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>45807</v>
+        <v>45971</v>
       </c>
       <c r="G80" t="n">
-        <v>570</v>
-      </c>
-      <c r="H80" t="n">
-        <v>2025</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Глуховская (Мамонтова) Анна Дмитриевна</t>
+          <t>Гукун Галина Владимировна</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>45280</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>45784</v>
+        <v>46035</v>
       </c>
       <c r="G81" t="n">
-        <v>504</v>
-      </c>
-      <c r="H81" t="n">
-        <v>2025</v>
+        <v>274</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Нуянзина Мила Андреевна</t>
+          <t xml:space="preserve">Бердибек кызы Альбина </t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5641,26 +5039,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>45272</v>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>45777</v>
+        <v>46062</v>
       </c>
       <c r="G82" t="n">
-        <v>505</v>
-      </c>
-      <c r="H82" t="n">
-        <v>2025</v>
+        <v>247</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Загнитковская Арина</t>
+          <t>Соколовский Ярослав</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5675,31 +5067,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>45523</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>45852</v>
+        <v>46097</v>
       </c>
       <c r="G83" t="n">
-        <v>329</v>
-      </c>
-      <c r="H83" t="n">
-        <v>2025</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Кашулин Данил Сергеевич</t>
+          <t>Донец Дарья Константиновна</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5709,60 +5095,48 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>45887</v>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>45891</v>
+        <v>46133</v>
       </c>
       <c r="G84" t="n">
-        <v>4</v>
-      </c>
-      <c r="H84" t="n">
-        <v>2025</v>
+        <v>176</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Корчикова Дарья Евгеньевна </t>
+          <t>Ефремова Алина Олеговна</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>45831</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>45901</v>
+        <v>46148</v>
       </c>
       <c r="G85" t="n">
-        <v>70</v>
-      </c>
-      <c r="H85" t="n">
-        <v>2025</v>
+        <v>161</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Новокшанов Егор Леонидович</t>
+          <t>Уалива Альмира Эдуардовна</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5772,99 +5146,81 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>45712</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>45901</v>
+        <v>46170</v>
       </c>
       <c r="G86" t="n">
-        <v>189</v>
-      </c>
-      <c r="H86" t="n">
-        <v>2025</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Тыщенко Анжелика Сергеевна</t>
+          <t>Артамонова Валерия Олеговна</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>45481</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>45904</v>
+        <v>46184</v>
       </c>
       <c r="G87" t="n">
-        <v>423</v>
-      </c>
-      <c r="H87" t="n">
-        <v>2025</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Кирнос Наталья</t>
+          <t>Прокаева Виктория Сергеевна</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>45544</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>45904</v>
+        <v>46189</v>
       </c>
       <c r="G88" t="n">
-        <v>360</v>
-      </c>
-      <c r="H88" t="n">
-        <v>2025</v>
+        <v>120</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Новокшанов Егор Леонидович</t>
+          <t>Кузьмин Матвей Игоревич</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5874,167 +5230,137 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>45712</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>45901</v>
+        <v>46211</v>
       </c>
       <c r="G89" t="n">
-        <v>189</v>
-      </c>
-      <c r="H89" t="n">
-        <v>2025</v>
+        <v>98</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Винтер Максим Генрихович</t>
+          <t xml:space="preserve">Гайдук Анна Евгеньевна </t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Вечерний менеджер</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>45775</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>45922</v>
+        <v>46203</v>
       </c>
       <c r="G90" t="n">
-        <v>147</v>
-      </c>
-      <c r="H90" t="n">
-        <v>2025</v>
+        <v>106</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Приходько Илья Олегович</t>
+          <t>Фролов Евгений Аркадьевич</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Вечерний менеджер</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>45351</v>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>45923</v>
+        <v>46203</v>
       </c>
       <c r="G91" t="n">
-        <v>572</v>
-      </c>
-      <c r="H91" t="n">
-        <v>2025</v>
+        <v>106</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Торден Дамиан </t>
+          <t xml:space="preserve">Есиков Глеб Русланович </t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Вечерний менеджер</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>45819</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>45929</v>
+        <v>46216</v>
       </c>
       <c r="G92" t="n">
-        <v>110</v>
-      </c>
-      <c r="H92" t="n">
-        <v>2025</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Винтер Максим Генрихович</t>
+          <t>Федоткина Наталья Евгеньевна</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>45775</v>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>45922</v>
+        <v>46223</v>
       </c>
       <c r="G93" t="n">
-        <v>147</v>
-      </c>
-      <c r="H93" t="n">
-        <v>2025</v>
+        <v>86</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Данькова Анастасия Сергеевна</t>
+          <t>Наливайко Арсений Ильич</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6044,167 +5370,137 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Вечерний менеджер</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>45894</v>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>45951</v>
+        <v>46244</v>
       </c>
       <c r="G94" t="n">
-        <v>57</v>
-      </c>
-      <c r="H94" t="n">
-        <v>2025</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Бураков Григорий Радиевич</t>
+          <t>Ибрагимова Анжелика Адалетовна</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>45772</v>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>45957</v>
+        <v>46244</v>
       </c>
       <c r="G95" t="n">
-        <v>185</v>
-      </c>
-      <c r="H95" t="n">
-        <v>2025</v>
+        <v>65</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Парфенова Анастасия Игоревна</t>
+          <t xml:space="preserve">Самарцев Захар Александрович </t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>45916</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>45968</v>
+        <v>46251</v>
       </c>
       <c r="G96" t="n">
-        <v>52</v>
-      </c>
-      <c r="H96" t="n">
-        <v>2025</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Монгуш Анай-Хаак Андреевна</t>
+          <t>Михеева Анна Сергеевна</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>45950</v>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>46001</v>
+        <v>46253</v>
       </c>
       <c r="G97" t="n">
-        <v>51</v>
-      </c>
-      <c r="H97" t="n">
-        <v>2025</v>
+        <v>56</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Смирнова Полина Ильинична</t>
+          <t>Лазар Ярослава Витальевна</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>45958</v>
-      </c>
-      <c r="F98" s="3" t="n">
-        <v>46017</v>
+        <v>46251</v>
       </c>
       <c r="G98" t="n">
-        <v>59</v>
-      </c>
-      <c r="H98" t="n">
-        <v>2025</v>
+        <v>58</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Федоринова София Владимировна</t>
+          <t>Гулько Эдуард Иванович</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6214,201 +5510,165 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>45908</v>
-      </c>
-      <c r="F99" s="3" t="n">
-        <v>46021</v>
+        <v>46258</v>
       </c>
       <c r="G99" t="n">
-        <v>113</v>
-      </c>
-      <c r="H99" t="n">
-        <v>2025</v>
+        <v>51</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Креймер Константин Андреевич</t>
+          <t>Васильева Анастасия Сергеевна</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>45944</v>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>46038</v>
+        <v>46258</v>
       </c>
       <c r="G100" t="n">
-        <v>94</v>
-      </c>
-      <c r="H100" t="n">
-        <v>2026</v>
+        <v>51</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Телков Данил Артемович</t>
+          <t>Ефременко Альбина Вадимовна</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>45791</v>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>46045</v>
+        <v>46265</v>
       </c>
       <c r="G101" t="n">
-        <v>254</v>
-      </c>
-      <c r="H101" t="n">
-        <v>2026</v>
+        <v>44</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Доржу Долума Шой-ооловна</t>
+          <t>Скрипкин Илья Павлович</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Вечерний менеджер</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>45880</v>
-      </c>
-      <c r="F102" s="3" t="n">
-        <v>46059</v>
+        <v>46265</v>
       </c>
       <c r="G102" t="n">
-        <v>179</v>
-      </c>
-      <c r="H102" t="n">
-        <v>2026</v>
+        <v>44</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Лаврентьева Ульяна Ивановна</t>
+          <t>Фомина Анастасия Юрьевна</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Вечерний менеджер</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>46036</v>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>46083</v>
+        <v>46280</v>
       </c>
       <c r="G103" t="n">
-        <v>47</v>
-      </c>
-      <c r="H103" t="n">
-        <v>2026</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Рыбников Бронислав Игоревич</t>
+          <t>Ворсина Елизавета Евгеньевна</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>46038</v>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>46080</v>
+        <v>46300</v>
       </c>
       <c r="G104" t="n">
-        <v>42</v>
-      </c>
-      <c r="H104" t="n">
-        <v>2026</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Домрачев Иван Дмитриевич</t>
+          <t>Ковалева Виктория Сергеевна</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6418,31 +5678,25 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Вечерний менеджер</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>46091</v>
-      </c>
-      <c r="F105" s="3" t="n">
-        <v>46097</v>
+        <v>46290</v>
       </c>
       <c r="G105" t="n">
-        <v>6</v>
-      </c>
-      <c r="H105" t="n">
-        <v>2026</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Хрипченко Анастасия Олеговна</t>
+          <t>Боброва Полина Сергеевна</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6452,65 +5706,53 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>45971</v>
-      </c>
-      <c r="F106" s="3" t="n">
-        <v>46099</v>
+        <v>46300</v>
       </c>
       <c r="G106" t="n">
-        <v>128</v>
-      </c>
-      <c r="H106" t="n">
-        <v>2026</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Кириченко Ангелина Вячеславовна</t>
+          <t>Ким Полина Александровна</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Специалист по бронированию</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>45771</v>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>46104</v>
+        <v>46307</v>
       </c>
       <c r="G107" t="n">
-        <v>333</v>
-      </c>
-      <c r="H107" t="n">
-        <v>2026</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ерыгин Евгений Игоревич</t>
+          <t xml:space="preserve">Лесничева Злата Александровна </t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6520,2318 +5762,74 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Отдел контроля поездок</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>45264</v>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>46112</v>
+        <v>46309</v>
       </c>
       <c r="G108" t="n">
-        <v>848</v>
-      </c>
-      <c r="H108" t="n">
-        <v>2026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Ооржак Нелли</t>
+          <t>Каратаев Александр Владимирович</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Руководитель/старший</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>44180</v>
-      </c>
-      <c r="F109" s="3" t="n">
-        <v>45762</v>
+        <v>46309</v>
       </c>
       <c r="G109" t="n">
-        <v>1582</v>
-      </c>
-      <c r="H109" t="n">
-        <v>2025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шивлякова Мария </t>
+          <t>Ткачук Диана</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Вечерний менеджер</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Уволен</t>
+          <t>Работает</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>46128</v>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>46133</v>
+        <v>46314</v>
       </c>
       <c r="G110" t="n">
-        <v>5</v>
-      </c>
-      <c r="H110" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Савкин Глеб Петрович </t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>45939</v>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>46141</v>
-      </c>
-      <c r="G111" t="n">
-        <v>202</v>
-      </c>
-      <c r="H111" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Ковалева Виктория Сергеевна</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>45945</v>
-      </c>
-      <c r="F112" s="3" t="n">
-        <v>46140</v>
-      </c>
-      <c r="G112" t="n">
-        <v>195</v>
-      </c>
-      <c r="H112" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Монгуш Тензин</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Специалист по бронированию</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>45589</v>
-      </c>
-      <c r="F113" s="3" t="n">
-        <v>46142</v>
-      </c>
-      <c r="G113" t="n">
-        <v>553</v>
-      </c>
-      <c r="H113" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Чернятьева Рина Витальевна </t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>46077</v>
-      </c>
-      <c r="F114" s="3" t="n">
-        <v>46146</v>
-      </c>
-      <c r="G114" t="n">
-        <v>69</v>
-      </c>
-      <c r="H114" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Карпова Валерия константиновна</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>45890</v>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>46147</v>
-      </c>
-      <c r="G115" t="n">
-        <v>257</v>
-      </c>
-      <c r="H115" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Кладов Антон Павлович</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>46133</v>
-      </c>
-      <c r="F116" s="3" t="n">
-        <v>46161</v>
-      </c>
-      <c r="G116" t="n">
-        <v>28</v>
-      </c>
-      <c r="H116" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Черкасова Полина</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Специалист по бронированию</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>45749</v>
-      </c>
-      <c r="F117" s="3" t="n">
-        <v>46171</v>
-      </c>
-      <c r="G117" t="n">
-        <v>422</v>
-      </c>
-      <c r="H117" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Резинкина Анастасия</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>46162</v>
-      </c>
-      <c r="F118" s="3" t="n">
-        <v>46183</v>
-      </c>
-      <c r="G118" t="n">
-        <v>21</v>
-      </c>
-      <c r="H118" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Рожнева Елизавета</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>45272</v>
-      </c>
-      <c r="F119" s="3" t="n">
-        <v>46181</v>
-      </c>
-      <c r="G119" t="n">
-        <v>909</v>
-      </c>
-      <c r="H119" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Чудинова Полина Владимировна  </t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Специалист по бронированию</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>45880</v>
-      </c>
-      <c r="F120" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="G120" t="n">
-        <v>298</v>
-      </c>
-      <c r="H120" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Самодурова Арина</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>46164</v>
-      </c>
-      <c r="F121" s="3" t="n">
-        <v>46188</v>
-      </c>
-      <c r="G121" t="n">
-        <v>24</v>
-      </c>
-      <c r="H121" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Сыдыбаев Жалынбек Сыртбаевич</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>46181</v>
-      </c>
-      <c r="F122" s="3" t="n">
-        <v>46189</v>
-      </c>
-      <c r="G122" t="n">
-        <v>8</v>
-      </c>
-      <c r="H122" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Мищенко Михаил Витальевич</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>45966</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>46220</v>
-      </c>
-      <c r="G123" t="n">
-        <v>254</v>
-      </c>
-      <c r="H123" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Долгополова Елена Сергеевна</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>46174</v>
-      </c>
-      <c r="F124" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="G124" t="n">
-        <v>49</v>
-      </c>
-      <c r="H124" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Жигалёв Денис Евгеньевич</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>46203</v>
-      </c>
-      <c r="F125" s="3" t="n">
-        <v>46227</v>
-      </c>
-      <c r="G125" t="n">
-        <v>24</v>
-      </c>
-      <c r="H125" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Кочева Анна Алексеевна</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>46062</v>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>46227</v>
-      </c>
-      <c r="G126" t="n">
-        <v>165</v>
-      </c>
-      <c r="H126" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Гундарева Виктория Константиновна</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>46085</v>
-      </c>
-      <c r="F127" s="3" t="n">
-        <v>46234</v>
-      </c>
-      <c r="G127" t="n">
-        <v>149</v>
-      </c>
-      <c r="H127" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Сериккали Мадина</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>46237</v>
-      </c>
-      <c r="F128" s="3" t="n">
-        <v>46252</v>
-      </c>
-      <c r="G128" t="n">
-        <v>15</v>
-      </c>
-      <c r="H128" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Власов Тимофей Антонович</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>46266</v>
-      </c>
-      <c r="G129" t="n">
-        <v>8</v>
-      </c>
-      <c r="H129" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Троельникова Софья</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Специалист по бронированию</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>45733</v>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>46251</v>
-      </c>
-      <c r="G130" t="n">
-        <v>518</v>
-      </c>
-      <c r="H130" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Решетень Регина Федоровна</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>45329</v>
-      </c>
-      <c r="F131" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="G131" t="n">
-        <v>943</v>
-      </c>
-      <c r="H131" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Рябик Арина Александровна</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>45194</v>
-      </c>
-      <c r="G132" t="n">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Никитюк Леон</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>45287</v>
-      </c>
-      <c r="G133" t="n">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Берлин Аександра</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>45268</v>
-      </c>
-      <c r="G134" t="n">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Кузьменко Александра Константиновна</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Отдел контроля поездок</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>45383</v>
-      </c>
-      <c r="G135" t="n">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Сазонов Сергей Викторович</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>45390</v>
-      </c>
-      <c r="G136" t="n">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Белотурова Кристина Владимировна</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Логист отдела контроля</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>45481</v>
-      </c>
-      <c r="G137" t="n">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Кралинова Алена Алексеевна </t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>45502</v>
-      </c>
-      <c r="G138" t="n">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Русских Юлия</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>45520</v>
-      </c>
-      <c r="G139" t="n">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Светашова Анастасия Владимировна</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>45527</v>
-      </c>
-      <c r="G140" t="n">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Шакирзянова Куддусия</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>45616</v>
-      </c>
-      <c r="G141" t="n">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Краснов Сергей Витальевич</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>45775</v>
-      </c>
-      <c r="G142" t="n">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лемешев Филипп Игоревич </t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>45792</v>
-      </c>
-      <c r="G143" t="n">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Польховская Анастасия Алексеевна</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Специалист по бронированию</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>45834</v>
-      </c>
-      <c r="G144" t="n">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Яруткина Александра Константиновна </t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Специалист по бронированию</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>45839</v>
-      </c>
-      <c r="G145" t="n">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Голев Кирилл Андреевич</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>45845</v>
-      </c>
-      <c r="G146" t="n">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Сакирко Виктория Алексеевна</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>45838</v>
-      </c>
-      <c r="G147" t="n">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Лебёдка Богдан Константинович</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="n">
-        <v>45890</v>
-      </c>
-      <c r="G148" t="n">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Габазов Тимур Алиханович</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="n">
-        <v>45880</v>
-      </c>
-      <c r="G149" t="n">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Бобров Андрей Юрьевич</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="n">
-        <v>45930</v>
-      </c>
-      <c r="G150" t="n">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Матющенко Ксения Евгеньевна</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="n">
-        <v>45930</v>
-      </c>
-      <c r="G151" t="n">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Бахтина Виктория Александровна</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>45944</v>
-      </c>
-      <c r="G152" t="n">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Коркунова Дарья Витальевна</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="n">
-        <v>45958</v>
-      </c>
-      <c r="G153" t="n">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Московских Алёна Владимировна</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="n">
-        <v>45945</v>
-      </c>
-      <c r="G154" t="n">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Петрова Евгения Вячеславовна</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="n">
-        <v>45971</v>
-      </c>
-      <c r="G155" t="n">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Гукун Галина Владимировна</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="n">
-        <v>46035</v>
-      </c>
-      <c r="G156" t="n">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Бердибек кызы Альбина </t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="n">
-        <v>46062</v>
-      </c>
-      <c r="G157" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Соколовский Ярослав</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E158" s="3" t="n">
-        <v>46097</v>
-      </c>
-      <c r="G158" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Донец Дарья Константиновна</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="n">
-        <v>46133</v>
-      </c>
-      <c r="G159" t="n">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Ефремова Алина Олеговна</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="n">
-        <v>46148</v>
-      </c>
-      <c r="G160" t="n">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Уалива Альмира Эдуардовна</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E161" s="3" t="n">
-        <v>46170</v>
-      </c>
-      <c r="G161" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Артамонова Валерия Олеговна</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="n">
-        <v>46184</v>
-      </c>
-      <c r="G162" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Прокаева Виктория Сергеевна</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>46189</v>
-      </c>
-      <c r="G163" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Кузьмин Матвей Игоревич</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="n">
-        <v>46211</v>
-      </c>
-      <c r="G164" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Гайдук Анна Евгеньевна </t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Вечерний менеджер</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="n">
-        <v>46203</v>
-      </c>
-      <c r="G165" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Фролов Евгений Аркадьевич</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Вечерний менеджер</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="n">
-        <v>46203</v>
-      </c>
-      <c r="G166" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Есиков Глеб Русланович </t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Вечерний менеджер</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="n">
-        <v>46216</v>
-      </c>
-      <c r="G167" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Федоткина Наталья Евгеньевна</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="G168" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Наливайко Арсений Ильич</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Вечерний менеджер</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="G169" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Ибрагимова Анжелика Адалетовна</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="G170" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Самарцев Захар Александрович </t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="n">
-        <v>46251</v>
-      </c>
-      <c r="G171" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Михеева Анна Сергеевна</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="n">
-        <v>46253</v>
-      </c>
-      <c r="G172" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Лазар Ярослава Витальевна</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="n">
-        <v>46251</v>
-      </c>
-      <c r="G173" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Гулько Эдуард Иванович</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="G174" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Васильева Анастасия Сергеевна</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="G175" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Ефременко Альбина Вадимовна</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="G176" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Скрипкин Илья Павлович</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Вечерний менеджер</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="G177" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Фомина Анастасия Юрьевна</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Вечерний менеджер</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="G178" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Ворсина Елизавета Евгеньевна</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="n">
-        <v>46300</v>
-      </c>
-      <c r="G179" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Ковалева Виктория Сергеевна</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Вечерний менеджер</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="G180" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Боброва Полина Сергеевна</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="n">
-        <v>46300</v>
-      </c>
-      <c r="G181" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Ким Полина Александровна</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="n">
-        <v>46307</v>
-      </c>
-      <c r="G182" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лесничева Злата Александровна </t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="n">
-        <v>46309</v>
-      </c>
-      <c r="G183" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Каратаев Александр Владимирович</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="n">
-        <v>46309</v>
-      </c>
-      <c r="G184" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Ткачук Диана</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Вечерний менеджер</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Работает</t>
-        </is>
-      </c>
-      <c r="E185" s="3" t="n">
-        <v>46314</v>
-      </c>
-      <c r="G185" t="n">
         <v>-5</v>
       </c>
     </row>

--- a/srok_raboty_bronirovanie_kontrol.xlsx
+++ b/srok_raboty_bronirovanie_kontrol.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По должностям (ушли)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Срез на дату" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Когорты найма" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Медиана для графика" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Количество для графика" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Отделы по годам" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Действующие" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все записи" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Разбивка (менеджеры)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По должностям (ушли)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Срез на дату" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Когорты найма" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Медиана для графика" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Количество для графика" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Отделы по годам" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Действующие" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все записи" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1053,11 +1054,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1068,37 +1079,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Должность</t>
+          <t>Год найма</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Год ухода</t>
+          <t>Принято</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Ушло</t>
+          <t>Работают</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Средний срок, дн</t>
+          <t>% работают</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Медиана, дн</t>
+          <t>Ушли</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Ушли &lt;90 дн</t>
+          <t>до 3 дней</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>% &lt;90 дн</t>
+          <t>4–7 дней</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>8–30 дней</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>31–60 дней</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>61–180 дней</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>больше 6 мес.</t>
         </is>
       </c>
     </row>
@@ -1108,28 +1139,38 @@
           <t>Бронирование</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
+      <c r="B2" t="n">
+        <v>2024</v>
       </c>
       <c r="C2" t="n">
-        <v>2024</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E2" t="n">
-        <v>63</v>
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.14</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0.7</v>
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1138,28 +1179,38 @@
           <t>Бронирование</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>2025</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>269</v>
+      <c r="E3" s="2" t="n">
+        <v>0.6</v>
       </c>
       <c r="F3" t="n">
-        <v>360</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>0.33</v>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1168,28 +1219,38 @@
           <t>Бронирование</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
+      <c r="B4" t="n">
+        <v>2026</v>
       </c>
       <c r="C4" t="n">
-        <v>2026</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="n">
-        <v>77</v>
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.68</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0.7</v>
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1198,28 +1259,38 @@
           <t>Контроль</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
+      <c r="B5" t="n">
+        <v>2024</v>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>54</v>
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.19</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>0.83</v>
+      <c r="L5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1228,28 +1299,38 @@
           <t>Контроль</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
+      <c r="B6" t="n">
+        <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>2025</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F6" t="n">
         <v>20</v>
       </c>
-      <c r="E6" t="n">
-        <v>137</v>
-      </c>
-      <c r="F6" t="n">
-        <v>110</v>
-      </c>
       <c r="G6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.35</v>
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1258,58 +1339,583 @@
           <t>Контроль</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
+      <c r="B7" t="n">
+        <v>2026</v>
       </c>
       <c r="C7" t="n">
-        <v>2026</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
       </c>
-      <c r="E7" t="n">
-        <v>130</v>
+      <c r="E7" s="2" t="n">
+        <v>0.65</v>
       </c>
       <c r="F7" t="n">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0.36</v>
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
+          <t>Оба отдела</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2024</v>
       </c>
       <c r="C8" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Оба отдела</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C9" t="n">
+        <v>34</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Оба отдела</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>2026</v>
       </c>
-      <c r="D8" t="n">
+      <c r="C10" t="n">
+        <v>45</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F10" t="n">
+        <v>15</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Самый успешный найм (по числу оставшихся)</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+      <c r="H12" s="1" t="n"/>
+      <c r="I12" s="1" t="n"/>
+      <c r="J12" s="1" t="n"/>
+      <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>по числу: 2026 (19 из 28)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>по доле: 2026 (68%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>по числу: 2026 (11 из 17)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>по доле: 2026 (65%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Оба отдела</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>по числу: 2026 (30 из 45)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>по доле: 2026 (67%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Отдел</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Год ухода</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Ушло</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr"/>
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" s="1" t="inlineStr"/>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>до 3 дней</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>4–7 дней</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>8–30 дней</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>31–60 дней</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr">
+        <is>
+          <t>61–180 дней</t>
+        </is>
+      </c>
+      <c r="L17" s="1" t="inlineStr">
+        <is>
+          <t>больше 6 мес.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C23" t="n">
+        <v>13</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Оба отдела</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C24" t="n">
+        <v>16</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Оба отдела</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C25" t="n">
+        <v>23</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Оба отдела</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C26" t="n">
+        <v>23</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1323,8 +1929,278 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Отдел</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Должность</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Год ухода</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ушло</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Средний срок, дн</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Медиана, дн</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ушли &lt;90 дн</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>% &lt;90 дн</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>269</v>
+      </c>
+      <c r="F3" t="n">
+        <v>360</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>77</v>
+      </c>
+      <c r="F4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>54</v>
+      </c>
+      <c r="F5" t="n">
+        <v>38</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>137</v>
+      </c>
+      <c r="F6" t="n">
+        <v>110</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="n">
+        <v>130</v>
+      </c>
+      <c r="F7" t="n">
+        <v>128</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -1620,14 +2496,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -1872,14 +2748,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -1941,89 +2817,6 @@
       </c>
       <c r="D4" t="n">
         <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Должность</t>
-        </is>
-      </c>
-      <c r="B1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D1" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Бронирование: Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Контроль: Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Контроль: Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2038,8 +2831,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -2048,7 +2841,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Отдел</t>
+          <t>Должность</t>
         </is>
       </c>
       <c r="B1" t="n">
@@ -2064,33 +2857,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Бронирование (медиана, дн)</t>
+          <t>Бронирование: Менеджер (основной)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>360</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Контроль (медиана, дн)</t>
+          <t>Контроль: Менеджер (основной)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>94</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Контроль: Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2105,8 +2914,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -2118,239 +2927,51 @@
           <t>Отдел</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Должность</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Год найма</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Человек</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Средний срок, дн</t>
-        </is>
+      <c r="B1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D1" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Вечерний менеджер</t>
-        </is>
+          <t>Бронирование (медиана, дн)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>2026</v>
+        <v>360</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E2" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
+          <t>Контроль (медиана, дн)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>2024</v>
+        <v>110</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Вечерний менеджер</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9</v>
-      </c>
-      <c r="E9" t="n">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>31</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2360,8 +2981,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H110"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -2370,6 +2991,261 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Отдел</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Должность</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Год найма</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Человек</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Средний срок, дн</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H110"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>ФИО</t>
         </is>
       </c>

--- a/srok_raboty_bronirovanie_kontrol.xlsx
+++ b/srok_raboty_bronirovanie_kontrol.xlsx
@@ -7,15 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Разбивка (менеджеры)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По должностям (ушли)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Срез на дату" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Когорты найма" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Медиана для графика" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Количество для графика" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Отделы по годам" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Действующие" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все записи" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По должностям (ушли)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Срез на дату" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Когорты найма" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Медиана для графика" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Количество для графика" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Отделы по годам" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Действующие" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все записи" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1054,21 +1053,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1079,57 +1068,37 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Год найма</t>
+          <t>Должность</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Принято</t>
+          <t>Год ухода</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Работают</t>
+          <t>Ушло</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>% работают</t>
+          <t>Средний срок, дн</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Ушли</t>
+          <t>Медиана, дн</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>до 3 дней</t>
+          <t>Ушли &lt;90 дн</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>4–7 дней</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>8–30 дней</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>31–60 дней</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>61–180 дней</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>больше 6 мес.</t>
+          <t>% &lt;90 дн</t>
         </is>
       </c>
     </row>
@@ -1139,38 +1108,28 @@
           <t>Бронирование</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>2024</v>
       </c>
-      <c r="C2" t="n">
-        <v>14</v>
-      </c>
       <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.14</v>
+        <v>11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>58</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.73</v>
       </c>
     </row>
     <row r="3">
@@ -1179,38 +1138,28 @@
           <t>Бронирование</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>2025</v>
       </c>
-      <c r="C3" t="n">
-        <v>5</v>
-      </c>
       <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.6</v>
+        <v>13</v>
+      </c>
+      <c r="E3" t="n">
+        <v>129</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="4">
@@ -1219,38 +1168,28 @@
           <t>Бронирование</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>2026</v>
       </c>
-      <c r="C4" t="n">
-        <v>28</v>
-      </c>
       <c r="D4" t="n">
-        <v>19</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.68</v>
+        <v>15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>193</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.47</v>
       </c>
     </row>
     <row r="5">
@@ -1259,38 +1198,28 @@
           <t>Контроль</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>2024</v>
       </c>
-      <c r="C5" t="n">
-        <v>16</v>
-      </c>
       <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.19</v>
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>54</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
         <v>5</v>
       </c>
-      <c r="L5" t="n">
-        <v>4</v>
+      <c r="H5" s="2" t="n">
+        <v>0.83</v>
       </c>
     </row>
     <row r="6">
@@ -1299,38 +1228,28 @@
           <t>Контроль</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>2025</v>
       </c>
-      <c r="C6" t="n">
-        <v>29</v>
-      </c>
       <c r="D6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.31</v>
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>137</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>9</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="7">
@@ -1339,583 +1258,58 @@
           <t>Контроль</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>2026</v>
-      </c>
-      <c r="C7" t="n">
-        <v>17</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>0.65</v>
+      <c r="E7" t="n">
+        <v>130</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Оба отдела</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2024</v>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>2026</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0.17</v>
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>9</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Оба отдела</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C9" t="n">
-        <v>34</v>
-      </c>
-      <c r="D9" t="n">
-        <v>12</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F9" t="n">
-        <v>22</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Оба отдела</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C10" t="n">
-        <v>45</v>
-      </c>
-      <c r="D10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="F10" t="n">
-        <v>15</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Самый успешный найм (по числу оставшихся)</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="n"/>
-      <c r="C12" s="1" t="n"/>
-      <c r="D12" s="1" t="n"/>
-      <c r="E12" s="1" t="n"/>
-      <c r="F12" s="1" t="n"/>
-      <c r="G12" s="1" t="n"/>
-      <c r="H12" s="1" t="n"/>
-      <c r="I12" s="1" t="n"/>
-      <c r="J12" s="1" t="n"/>
-      <c r="K12" s="1" t="n"/>
-      <c r="L12" s="1" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>по числу: 2026 (19 из 28)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>по доле: 2026 (68%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>по числу: 2026 (11 из 17)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>по доле: 2026 (65%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Оба отдела</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>по числу: 2026 (30 из 45)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>по доле: 2026 (67%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Отдел</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>Год ухода</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>Ушло</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr"/>
-      <c r="E17" s="1" t="inlineStr"/>
-      <c r="F17" s="1" t="inlineStr"/>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>до 3 дней</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t>4–7 дней</t>
-        </is>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>8–30 дней</t>
-        </is>
-      </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>31–60 дней</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>61–180 дней</t>
-        </is>
-      </c>
-      <c r="L17" s="1" t="inlineStr">
-        <is>
-          <t>больше 6 мес.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C18" t="n">
-        <v>10</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C20" t="n">
-        <v>10</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C21" t="n">
-        <v>6</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C22" t="n">
-        <v>20</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4</v>
-      </c>
-      <c r="K22" t="n">
-        <v>9</v>
-      </c>
-      <c r="L22" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C23" t="n">
-        <v>13</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Оба отдела</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C24" t="n">
-        <v>16</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>6</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Оба отдела</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C25" t="n">
-        <v>23</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K25" t="n">
-        <v>9</v>
-      </c>
-      <c r="L25" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Оба отдела</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C26" t="n">
-        <v>23</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" t="n">
-        <v>7</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>6</v>
-      </c>
-      <c r="L26" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1929,278 +1323,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Отдел</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Должность</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Год ухода</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Ушло</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Средний срок, дн</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Медиана, дн</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Ушли &lt;90 дн</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>% &lt;90 дн</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E2" t="n">
-        <v>63</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>269</v>
-      </c>
-      <c r="F3" t="n">
-        <v>360</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="n">
-        <v>77</v>
-      </c>
-      <c r="F4" t="n">
-        <v>35</v>
-      </c>
-      <c r="G4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>54</v>
-      </c>
-      <c r="F5" t="n">
-        <v>38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D6" t="n">
-        <v>20</v>
-      </c>
-      <c r="E6" t="n">
-        <v>137</v>
-      </c>
-      <c r="F6" t="n">
-        <v>110</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D7" t="n">
-        <v>11</v>
-      </c>
-      <c r="E7" t="n">
-        <v>130</v>
-      </c>
-      <c r="F7" t="n">
-        <v>128</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -2259,16 +1383,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="E2" t="n">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -2313,16 +1437,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E4" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -2340,19 +1464,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="E5" t="n">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="6">
@@ -2394,19 +1518,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="E7" t="n">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="8">
@@ -2421,19 +1545,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="E8" t="n">
         <v>106</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="9">
@@ -2475,19 +1599,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="E10" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
@@ -2496,14 +1620,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -2555,16 +1679,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F2" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3">
@@ -2599,16 +1723,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F4" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5">
@@ -2621,16 +1745,16 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
       <c r="E5" s="2" t="n">
-        <v>0.6</v>
+        <v>0.24</v>
       </c>
       <c r="F5" t="n">
-        <v>299</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6">
@@ -2665,16 +1789,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="F7" t="n">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8">
@@ -2745,6 +1869,83 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Должность</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D1" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Бронирование: Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D2" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Контроль: Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>38</v>
+      </c>
+      <c r="C3" t="n">
+        <v>110</v>
+      </c>
+      <c r="D3" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Контроль: Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2755,7 +1956,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -2784,13 +1985,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>360</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2800,13 +2001,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>128</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -2815,8 +2016,14 @@
           <t>Контроль: Менеджер 2/2</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2831,8 +2038,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -2841,7 +2048,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Должность</t>
+          <t>Отдел</t>
         </is>
       </c>
       <c r="B1" t="n">
@@ -2857,49 +2064,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Бронирование: Менеджер (основной)</t>
+          <t>Бронирование (медиана, дн)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Контроль: Менеджер (основной)</t>
+          <t>Контроль (медиана, дн)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Контроль: Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2914,8 +2105,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -2927,51 +2118,239 @@
           <t>Отдел</t>
         </is>
       </c>
-      <c r="B1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D1" t="n">
-        <v>2026</v>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Должность</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Год найма</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Человек</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Средний срок, дн</t>
+        </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Бронирование (медиана, дн)</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>44</v>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>360</v>
+        <v>2026</v>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Контроль (медиана, дн)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>38</v>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>110</v>
+        <v>2024</v>
       </c>
       <c r="D3" t="n">
-        <v>94</v>
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2981,8 +2360,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:H128"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -2991,609 +2370,354 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>ФИО</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Отдел</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Должность</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Год найма</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Человек</t>
+          <t>Статус</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Средний срок, дн</t>
+          <t>Принят</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Уволен</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Срок, дн</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Год ухода</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Дуйшенкул кызы Эрке</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E2" t="n">
-        <v>63</v>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Уволен</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>45315</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>45350</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2024</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Морозова Кристина Александровна</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Уволен</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>45426</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>45436</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
         <v>2024</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>850</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Ховалыг Дан-Хаяа Шолбановна</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>392</v>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Уволен</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>45468</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>45488</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2024</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Удалова Виктория</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>209</v>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Уволен</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>45481</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>45497</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2024</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Акимова Анастасия Константиновна</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" t="n">
-        <v>73</v>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Уволен</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>45474</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>45526</v>
+      </c>
+      <c r="G6" t="n">
+        <v>52</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2024</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Нахтигаль Глеб Сергеевич</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>19</v>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Уволен</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>45511</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>45517</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2024</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Коми Надежда Геннадьевна</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Уволен</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>45488</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>45560</v>
+      </c>
+      <c r="G8" t="n">
+        <v>72</v>
+      </c>
+      <c r="H8" t="n">
         <v>2024</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>763</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Червинская Виктория</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9</v>
-      </c>
-      <c r="E9" t="n">
-        <v>426</v>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Уволен</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>45567</v>
+      </c>
+      <c r="G9" t="n">
+        <v>23</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2024</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Карлин Иван</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>186</v>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Уволен</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>45544</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>45572</v>
+      </c>
+      <c r="G10" t="n">
+        <v>28</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2024</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Менеджер 2/2</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H110"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ФИО</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Отдел</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Должность</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Статус</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Принят</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Срок, дн</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Год ухода</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Дуйшенкул кызы Эрке</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>45315</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>45350</v>
-      </c>
-      <c r="G2" t="n">
-        <v>35</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Морозова Кристина Александровна</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>45426</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>45436</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ховалыг Дан-Хаяа Шолбановна</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>45468</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>45488</v>
-      </c>
-      <c r="G4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Удалова Виктория</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>45481</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>45497</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Акимова Анастасия Константиновна</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>45474</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>45526</v>
-      </c>
-      <c r="G6" t="n">
-        <v>52</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Нахтигаль Глеб Сергеевич</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Контроль</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>45511</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>45517</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Коми Надежда Геннадьевна</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>45488</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>45560</v>
-      </c>
-      <c r="G8" t="n">
-        <v>72</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Червинская Виктория</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>45544</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>45567</v>
-      </c>
-      <c r="G9" t="n">
-        <v>23</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Карлин Иван</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Менеджер (основной)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Уволен</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>45544</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>45572</v>
-      </c>
-      <c r="G10" t="n">
-        <v>28</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>Егембердиев Тимур</t>
         </is>
       </c>
@@ -3764,12 +2888,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Микрюков Олег </t>
+          <t>Минина Алена</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3783,13 +2907,13 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>45495</v>
+        <v>45628</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>45652</v>
+        <v>45638</v>
       </c>
       <c r="G16" t="n">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
         <v>2024</v>
@@ -3798,12 +2922,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Петрушина Александра</t>
+          <t xml:space="preserve">Микрюков Олег </t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3817,13 +2941,13 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>45544</v>
+        <v>45495</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>45654</v>
+        <v>45652</v>
       </c>
       <c r="G17" t="n">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="H17" t="n">
         <v>2024</v>
@@ -3832,12 +2956,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Тильга Александра</t>
+          <t>Петрушина Александра</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3851,22 +2975,22 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>45623</v>
+        <v>45544</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>45699</v>
+        <v>45654</v>
       </c>
       <c r="G18" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="H18" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Баздылев Иван</t>
+          <t>Тильга Александра</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3888,10 +3012,10 @@
         <v>45623</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>45716</v>
+        <v>45699</v>
       </c>
       <c r="G19" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H19" t="n">
         <v>2025</v>
@@ -3900,12 +3024,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Лепехина Диана</t>
+          <t xml:space="preserve">Шостенко Артём </t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3919,13 +3043,13 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>45531</v>
+        <v>45671</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>45734</v>
+        <v>45705</v>
       </c>
       <c r="G20" t="n">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="H20" t="n">
         <v>2025</v>
@@ -3934,7 +3058,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Константинов Павел</t>
+          <t>Баздылев Иван</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3953,13 +3077,13 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>45726</v>
+        <v>45623</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>45755</v>
+        <v>45716</v>
       </c>
       <c r="G21" t="n">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="H21" t="n">
         <v>2025</v>
@@ -3968,7 +3092,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Гребенщикова Софья</t>
+          <t>Лепехина Диана</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3987,13 +3111,13 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>45650</v>
+        <v>45531</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>45789</v>
+        <v>45734</v>
       </c>
       <c r="G22" t="n">
-        <v>139</v>
+        <v>203</v>
       </c>
       <c r="H22" t="n">
         <v>2025</v>
@@ -4002,12 +3126,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Березуцкая Светлана</t>
+          <t>Константинов Павел</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4021,13 +3145,13 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>45454</v>
+        <v>45726</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>45842</v>
+        <v>45755</v>
       </c>
       <c r="G23" t="n">
-        <v>388</v>
+        <v>29</v>
       </c>
       <c r="H23" t="n">
         <v>2025</v>
@@ -4036,12 +3160,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Загнитковская Арина</t>
+          <t>Косицын Никита</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4055,13 +3179,13 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>45523</v>
+        <v>45726</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>45852</v>
+        <v>45762</v>
       </c>
       <c r="G24" t="n">
-        <v>329</v>
+        <v>36</v>
       </c>
       <c r="H24" t="n">
         <v>2025</v>
@@ -4070,7 +3194,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Степанов Тимофей</t>
+          <t>Гребенщикова Софья</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4089,13 +3213,13 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>45749</v>
+        <v>45650</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>45854</v>
+        <v>45789</v>
       </c>
       <c r="G25" t="n">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="H25" t="n">
         <v>2025</v>
@@ -4104,12 +3228,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Герасименко Илья</t>
+          <t>Прожерина Кристина</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4123,13 +3247,13 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>45810</v>
+        <v>45735</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>45854</v>
+        <v>45799</v>
       </c>
       <c r="G26" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H26" t="n">
         <v>2025</v>
@@ -4138,12 +3262,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ткаченко Виктория</t>
+          <t xml:space="preserve">Цунаев Олег </t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4157,13 +3281,13 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>45757</v>
+        <v>45671</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>45868</v>
+        <v>45835</v>
       </c>
       <c r="G27" t="n">
-        <v>111</v>
+        <v>164</v>
       </c>
       <c r="H27" t="n">
         <v>2025</v>
@@ -4172,12 +3296,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Каминицкас Альгис Витальевич</t>
+          <t>Березуцкая Светлана</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4191,13 +3315,13 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>45841</v>
+        <v>45454</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>45882</v>
+        <v>45842</v>
       </c>
       <c r="G28" t="n">
-        <v>41</v>
+        <v>388</v>
       </c>
       <c r="H28" t="n">
         <v>2025</v>
@@ -4240,12 +3364,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Кашулин Данил Сергеевич</t>
+          <t>Тимофеев Никита Сергеевич</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4259,13 +3383,13 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>45887</v>
+        <v>45834</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>45891</v>
+        <v>45847</v>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H30" t="n">
         <v>2025</v>
@@ -4274,7 +3398,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Тыщенко Анжелика Сергеевна</t>
+          <t>Степанов Тимофей</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4293,13 +3417,13 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>45481</v>
+        <v>45749</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>45904</v>
+        <v>45854</v>
       </c>
       <c r="G31" t="n">
-        <v>423</v>
+        <v>105</v>
       </c>
       <c r="H31" t="n">
         <v>2025</v>
@@ -4308,12 +3432,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Кирнос Наталья</t>
+          <t>Герасименко Илья</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4327,13 +3451,13 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>45544</v>
+        <v>45810</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>45904</v>
+        <v>45854</v>
       </c>
       <c r="G32" t="n">
-        <v>360</v>
+        <v>44</v>
       </c>
       <c r="H32" t="n">
         <v>2025</v>
@@ -4342,7 +3466,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Винтер Максим Генрихович</t>
+          <t>Ткаченко Виктория</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4361,13 +3485,13 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>45775</v>
+        <v>45757</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>45922</v>
+        <v>45868</v>
       </c>
       <c r="G33" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="H33" t="n">
         <v>2025</v>
@@ -4376,12 +3500,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Торден Дамиан </t>
+          <t>Бельтяева Анель</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4395,13 +3519,13 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>45819</v>
+        <v>45811</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>45929</v>
+        <v>45870</v>
       </c>
       <c r="G34" t="n">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="H34" t="n">
         <v>2025</v>
@@ -4410,7 +3534,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Винтер Максим Генрихович</t>
+          <t>Каминицкас Альгис Витальевич</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4429,13 +3553,13 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>45775</v>
+        <v>45841</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>45922</v>
+        <v>45882</v>
       </c>
       <c r="G35" t="n">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="H35" t="n">
         <v>2025</v>
@@ -4444,7 +3568,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Бураков Григорий Радиевич</t>
+          <t>Загнитковская Арина</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4463,13 +3587,13 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>45772</v>
+        <v>45523</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>45957</v>
+        <v>45852</v>
       </c>
       <c r="G36" t="n">
-        <v>185</v>
+        <v>329</v>
       </c>
       <c r="H36" t="n">
         <v>2025</v>
@@ -4478,7 +3602,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Парфенова Анастасия Игоревна</t>
+          <t>Кашулин Данил Сергеевич</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4497,13 +3621,13 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>45916</v>
+        <v>45887</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>45968</v>
+        <v>45891</v>
       </c>
       <c r="G37" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
         <v>2025</v>
@@ -4512,12 +3636,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Монгуш Анай-Хаак Андреевна</t>
+          <t xml:space="preserve">Корчикова Дарья Евгеньевна </t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4531,13 +3655,13 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>45950</v>
+        <v>45831</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>46001</v>
+        <v>45901</v>
       </c>
       <c r="G38" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="H38" t="n">
         <v>2025</v>
@@ -4546,7 +3670,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Смирнова Полина Ильинична</t>
+          <t>Новокшанов Егор Леонидович</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4565,13 +3689,13 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>45958</v>
+        <v>45712</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>46017</v>
+        <v>45901</v>
       </c>
       <c r="G39" t="n">
-        <v>59</v>
+        <v>189</v>
       </c>
       <c r="H39" t="n">
         <v>2025</v>
@@ -4580,7 +3704,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Федоринова София Владимировна</t>
+          <t>Тыщенко Анжелика Сергеевна</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4599,13 +3723,13 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>45908</v>
+        <v>45481</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>46021</v>
+        <v>45904</v>
       </c>
       <c r="G40" t="n">
-        <v>113</v>
+        <v>423</v>
       </c>
       <c r="H40" t="n">
         <v>2025</v>
@@ -4614,12 +3738,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Креймер Константин Андреевич</t>
+          <t>Кирнос Наталья</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4633,27 +3757,27 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>45944</v>
+        <v>45544</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>46038</v>
+        <v>45904</v>
       </c>
       <c r="G41" t="n">
-        <v>94</v>
+        <v>360</v>
       </c>
       <c r="H41" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Телков Данил Артемович</t>
+          <t>Новокшанов Егор Леонидович</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4667,22 +3791,22 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>45791</v>
+        <v>45712</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>46045</v>
+        <v>45901</v>
       </c>
       <c r="G42" t="n">
-        <v>254</v>
+        <v>189</v>
       </c>
       <c r="H42" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Доржу Долума Шой-ооловна</t>
+          <t>Винтер Максим Генрихович</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4701,22 +3825,22 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>45880</v>
+        <v>45775</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>46059</v>
+        <v>45922</v>
       </c>
       <c r="G43" t="n">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="H43" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Лаврентьева Ульяна Ивановна</t>
+          <t xml:space="preserve">Торден Дамиан </t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4735,27 +3859,27 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>46036</v>
+        <v>45819</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>46083</v>
+        <v>45929</v>
       </c>
       <c r="G44" t="n">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="H44" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Рыбников Бронислав Игоревич</t>
+          <t>Винтер Максим Генрихович</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4769,27 +3893,27 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>46038</v>
+        <v>45775</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>46080</v>
+        <v>45922</v>
       </c>
       <c r="G45" t="n">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="H45" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Домрачев Иван Дмитриевич</t>
+          <t>Данькова Анастасия Сергеевна</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4803,22 +3927,22 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>46091</v>
+        <v>45894</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>46097</v>
+        <v>45951</v>
       </c>
       <c r="G46" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="H46" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Хрипченко Анастасия Олеговна</t>
+          <t>Бураков Григорий Радиевич</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4837,22 +3961,22 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>45971</v>
+        <v>45772</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>46099</v>
+        <v>45957</v>
       </c>
       <c r="G47" t="n">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="H47" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шивлякова Мария </t>
+          <t>Парфенова Анастасия Игоревна</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4871,22 +3995,22 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>46128</v>
+        <v>45916</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>46133</v>
+        <v>45968</v>
       </c>
       <c r="G48" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="H48" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Савкин Глеб Петрович </t>
+          <t>Монгуш Анай-Хаак Андреевна</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4905,27 +4029,27 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>45939</v>
+        <v>45950</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>46141</v>
+        <v>46001</v>
       </c>
       <c r="G49" t="n">
-        <v>202</v>
+        <v>51</v>
       </c>
       <c r="H49" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ковалева Виктория Сергеевна</t>
+          <t>Смирнова Полина Ильинична</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4939,22 +4063,22 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>45945</v>
+        <v>45958</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>46140</v>
+        <v>46017</v>
       </c>
       <c r="G50" t="n">
-        <v>195</v>
+        <v>59</v>
       </c>
       <c r="H50" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чернятьева Рина Витальевна </t>
+          <t>Федоринова София Владимировна</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4973,27 +4097,27 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>46077</v>
+        <v>45908</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>46146</v>
+        <v>46021</v>
       </c>
       <c r="G51" t="n">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="H51" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Карпова Валерия константиновна</t>
+          <t>Креймер Константин Андреевич</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5007,13 +4131,13 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>45890</v>
+        <v>45944</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>46147</v>
+        <v>46038</v>
       </c>
       <c r="G52" t="n">
-        <v>257</v>
+        <v>94</v>
       </c>
       <c r="H52" t="n">
         <v>2026</v>
@@ -5022,12 +4146,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Кладов Антон Павлович</t>
+          <t>Телков Данил Артемович</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5041,13 +4165,13 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>46133</v>
+        <v>45791</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>46161</v>
+        <v>46045</v>
       </c>
       <c r="G53" t="n">
-        <v>28</v>
+        <v>254</v>
       </c>
       <c r="H53" t="n">
         <v>2026</v>
@@ -5056,12 +4180,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Резинкина Анастасия</t>
+          <t>Доржу Долума Шой-ооловна</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5075,13 +4199,13 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>46162</v>
+        <v>45880</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>46183</v>
+        <v>46059</v>
       </c>
       <c r="G54" t="n">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="H54" t="n">
         <v>2026</v>
@@ -5090,12 +4214,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Самодурова Арина</t>
+          <t>Лаврентьева Ульяна Ивановна</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5109,13 +4233,13 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>46164</v>
+        <v>46036</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>46188</v>
+        <v>46083</v>
       </c>
       <c r="G55" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="H55" t="n">
         <v>2026</v>
@@ -5124,7 +4248,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Сыдыбаев Жалынбек Сыртбаевич</t>
+          <t>Рыбников Бронислав Игоревич</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5143,13 +4267,13 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>46181</v>
+        <v>46038</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>46189</v>
+        <v>46080</v>
       </c>
       <c r="G56" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="H56" t="n">
         <v>2026</v>
@@ -5158,7 +4282,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Мищенко Михаил Витальевич</t>
+          <t>Домрачев Иван Дмитриевич</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5177,13 +4301,13 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>45966</v>
+        <v>46091</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>46220</v>
+        <v>46097</v>
       </c>
       <c r="G57" t="n">
-        <v>254</v>
+        <v>6</v>
       </c>
       <c r="H57" t="n">
         <v>2026</v>
@@ -5192,12 +4316,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Долгополова Елена Сергеевна</t>
+          <t>Хрипченко Анастасия Олеговна</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5211,13 +4335,13 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>46174</v>
+        <v>45971</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>46223</v>
+        <v>46099</v>
       </c>
       <c r="G58" t="n">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="H58" t="n">
         <v>2026</v>
@@ -5226,7 +4350,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Жигалёв Денис Евгеньевич</t>
+          <t>Кириченко Ангелина Вячеславовна</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5245,13 +4369,13 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>46203</v>
+        <v>45771</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>46227</v>
+        <v>46104</v>
       </c>
       <c r="G59" t="n">
-        <v>24</v>
+        <v>333</v>
       </c>
       <c r="H59" t="n">
         <v>2026</v>
@@ -5260,12 +4384,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Кочева Анна Алексеевна</t>
+          <t xml:space="preserve">Шивлякова Мария </t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5279,13 +4403,13 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>46062</v>
+        <v>46128</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>46227</v>
+        <v>46133</v>
       </c>
       <c r="G60" t="n">
-        <v>165</v>
+        <v>5</v>
       </c>
       <c r="H60" t="n">
         <v>2026</v>
@@ -5294,12 +4418,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Гундарева Виктория Константиновна</t>
+          <t xml:space="preserve">Савкин Глеб Петрович </t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5313,13 +4437,13 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>46085</v>
+        <v>45939</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>46234</v>
+        <v>46141</v>
       </c>
       <c r="G61" t="n">
-        <v>149</v>
+        <v>202</v>
       </c>
       <c r="H61" t="n">
         <v>2026</v>
@@ -5328,7 +4452,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Сериккали Мадина</t>
+          <t>Ковалева Виктория Сергеевна</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5338,7 +4462,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5347,13 +4471,13 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>46237</v>
+        <v>45945</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>46252</v>
+        <v>46140</v>
       </c>
       <c r="G62" t="n">
-        <v>15</v>
+        <v>195</v>
       </c>
       <c r="H62" t="n">
         <v>2026</v>
@@ -5362,17 +4486,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Власов Тимофей Антонович</t>
+          <t>Монгуш Тензин</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5381,13 +4505,13 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>46258</v>
+        <v>45589</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>46266</v>
+        <v>46142</v>
       </c>
       <c r="G63" t="n">
-        <v>8</v>
+        <v>553</v>
       </c>
       <c r="H63" t="n">
         <v>2026</v>
@@ -5396,12 +4520,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Сазонов Сергей Викторович</t>
+          <t xml:space="preserve">Чернятьева Рина Витальевна </t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5411,25 +4535,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>45390</v>
+        <v>46077</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>46146</v>
       </c>
       <c r="G64" t="n">
-        <v>919</v>
+        <v>69</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кралинова Алена Алексеевна </t>
+          <t>Карпова Валерия константиновна</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5439,25 +4569,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>45502</v>
+        <v>45890</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>46147</v>
       </c>
       <c r="G65" t="n">
-        <v>807</v>
+        <v>257</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Русских Юлия</t>
+          <t>Кладов Антон Павлович</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5467,20 +4603,26 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>45520</v>
+        <v>46133</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>46161</v>
       </c>
       <c r="G66" t="n">
-        <v>789</v>
+        <v>28</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Светашова Анастасия Владимировна</t>
+          <t>Черкасова Полина</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5495,25 +4637,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>45527</v>
+        <v>45749</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>46171</v>
       </c>
       <c r="G67" t="n">
-        <v>782</v>
+        <v>422</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Шакирзянова Куддусия</t>
+          <t>Резинкина Анастасия</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5523,25 +4671,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>45616</v>
+        <v>46162</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>46183</v>
       </c>
       <c r="G68" t="n">
-        <v>693</v>
+        <v>21</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Краснов Сергей Витальевич</t>
+          <t xml:space="preserve">Чудинова Полина Владимировна  </t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5551,25 +4705,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>45775</v>
+        <v>45880</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>46178</v>
       </c>
       <c r="G69" t="n">
-        <v>534</v>
+        <v>298</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лемешев Филипп Игоревич </t>
+          <t>Самодурова Арина</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5579,25 +4739,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>45792</v>
+        <v>46164</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>46188</v>
       </c>
       <c r="G70" t="n">
-        <v>517</v>
+        <v>24</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Голев Кирилл Андреевич</t>
+          <t>Сыдыбаев Жалынбек Сыртбаевич</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5607,20 +4773,26 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>45845</v>
+        <v>46181</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>46189</v>
       </c>
       <c r="G71" t="n">
-        <v>464</v>
+        <v>8</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Сакирко Виктория Алексеевна</t>
+          <t>Мищенко Михаил Витальевич</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5635,20 +4807,26 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>45838</v>
+        <v>45966</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>46220</v>
       </c>
       <c r="G72" t="n">
-        <v>471</v>
+        <v>254</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Лебёдка Богдан Константинович</t>
+          <t>Долгополова Елена Сергеевна</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5663,25 +4841,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>45890</v>
+        <v>46174</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>46223</v>
       </c>
       <c r="G73" t="n">
-        <v>419</v>
+        <v>49</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Габазов Тимур Алиханович</t>
+          <t>Жигалёв Денис Евгеньевич</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5691,20 +4875,26 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>45880</v>
+        <v>46203</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>46227</v>
       </c>
       <c r="G74" t="n">
-        <v>429</v>
+        <v>24</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Бобров Андрей Юрьевич</t>
+          <t>Кочева Анна Алексеевна</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5719,20 +4909,26 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>45930</v>
+        <v>46062</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>46227</v>
       </c>
       <c r="G75" t="n">
-        <v>379</v>
+        <v>165</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Матющенко Ксения Евгеньевна</t>
+          <t>Гундарева Виктория Константиновна</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5747,20 +4943,26 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>45930</v>
+        <v>46085</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>46234</v>
       </c>
       <c r="G76" t="n">
-        <v>379</v>
+        <v>149</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Бахтина Виктория Александровна</t>
+          <t>Сериккали Мадина</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5770,25 +4972,31 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>45944</v>
+        <v>46237</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>46252</v>
       </c>
       <c r="G77" t="n">
-        <v>365</v>
+        <v>15</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Коркунова Дарья Витальевна</t>
+          <t>Власов Тимофей Антонович</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5798,30 +5006,36 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>45958</v>
+        <v>46258</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>46266</v>
       </c>
       <c r="G78" t="n">
-        <v>351</v>
+        <v>8</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Московских Алёна Владимировна</t>
+          <t>Троельникова Софья</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5831,25 +5045,31 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>45945</v>
+        <v>45733</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>46251</v>
       </c>
       <c r="G79" t="n">
-        <v>364</v>
+        <v>518</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Петрова Евгения Вячеславовна</t>
+          <t>Сазонов Сергей Викторович</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5863,21 +5083,21 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>45971</v>
+        <v>45390</v>
       </c>
       <c r="G80" t="n">
-        <v>338</v>
+        <v>919</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Гукун Галина Владимировна</t>
+          <t xml:space="preserve">Кралинова Алена Алексеевна </t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5891,21 +5111,21 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>46035</v>
+        <v>45502</v>
       </c>
       <c r="G81" t="n">
-        <v>274</v>
+        <v>807</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бердибек кызы Альбина </t>
+          <t>Русских Юлия</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5919,21 +5139,21 @@
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>46062</v>
+        <v>45520</v>
       </c>
       <c r="G82" t="n">
-        <v>247</v>
+        <v>789</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Соколовский Ярослав</t>
+          <t>Светашова Анастасия Владимировна</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5947,21 +5167,21 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>46097</v>
+        <v>45527</v>
       </c>
       <c r="G83" t="n">
-        <v>212</v>
+        <v>782</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Донец Дарья Константиновна</t>
+          <t>Шакирзянова Куддусия</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5975,16 +5195,16 @@
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>46133</v>
+        <v>45616</v>
       </c>
       <c r="G84" t="n">
-        <v>176</v>
+        <v>693</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ефремова Алина Олеговна</t>
+          <t>Краснов Сергей Витальевич</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6003,21 +5223,21 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>46148</v>
+        <v>45775</v>
       </c>
       <c r="G85" t="n">
-        <v>161</v>
+        <v>534</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Уалива Альмира Эдуардовна</t>
+          <t xml:space="preserve">Лемешев Филипп Игоревич </t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6031,16 +5251,16 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>46170</v>
+        <v>45792</v>
       </c>
       <c r="G86" t="n">
-        <v>139</v>
+        <v>517</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Артамонова Валерия Олеговна</t>
+          <t>Польховская Анастасия Алексеевна</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6050,7 +5270,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6059,26 +5279,26 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>46184</v>
+        <v>45834</v>
       </c>
       <c r="G87" t="n">
-        <v>125</v>
+        <v>475</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Прокаева Виктория Сергеевна</t>
+          <t xml:space="preserve">Яруткина Александра Константиновна </t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6087,26 +5307,26 @@
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>46189</v>
+        <v>45839</v>
       </c>
       <c r="G88" t="n">
-        <v>120</v>
+        <v>470</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Кузьмин Матвей Игоревич</t>
+          <t>Голев Кирилл Андреевич</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6115,26 +5335,26 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>46211</v>
+        <v>45845</v>
       </c>
       <c r="G89" t="n">
-        <v>98</v>
+        <v>464</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Гайдук Анна Евгеньевна </t>
+          <t>Сакирко Виктория Алексеевна</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6143,16 +5363,16 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>46203</v>
+        <v>45838</v>
       </c>
       <c r="G90" t="n">
-        <v>106</v>
+        <v>471</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Фролов Евгений Аркадьевич</t>
+          <t>Лебёдка Богдан Константинович</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6162,7 +5382,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6171,26 +5391,26 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>46203</v>
+        <v>45890</v>
       </c>
       <c r="G91" t="n">
-        <v>106</v>
+        <v>419</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Есиков Глеб Русланович </t>
+          <t>Габазов Тимур Алиханович</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6199,16 +5419,16 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>46216</v>
+        <v>45880</v>
       </c>
       <c r="G92" t="n">
-        <v>93</v>
+        <v>429</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Федоткина Наталья Евгеньевна</t>
+          <t>Бобров Андрей Юрьевич</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6218,7 +5438,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6227,16 +5447,16 @@
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>46223</v>
+        <v>45930</v>
       </c>
       <c r="G93" t="n">
-        <v>86</v>
+        <v>379</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Наливайко Арсений Ильич</t>
+          <t>Матющенко Ксения Евгеньевна</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6246,7 +5466,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6255,26 +5475,26 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>46244</v>
+        <v>45930</v>
       </c>
       <c r="G94" t="n">
-        <v>65</v>
+        <v>379</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ибрагимова Анжелика Адалетовна</t>
+          <t>Бахтина Виктория Александровна</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6283,26 +5503,26 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>46244</v>
+        <v>45944</v>
       </c>
       <c r="G95" t="n">
-        <v>65</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Самарцев Захар Александрович </t>
+          <t>Коркунова Дарья Витальевна</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6311,26 +5531,26 @@
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>46251</v>
+        <v>45958</v>
       </c>
       <c r="G96" t="n">
-        <v>58</v>
+        <v>351</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Михеева Анна Сергеевна</t>
+          <t>Московских Алёна Владимировна</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6339,16 +5559,16 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>46253</v>
+        <v>45945</v>
       </c>
       <c r="G97" t="n">
-        <v>56</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Лазар Ярослава Витальевна</t>
+          <t>Петрова Евгения Вячеславовна</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6358,7 +5578,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6367,26 +5587,26 @@
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>46251</v>
+        <v>45971</v>
       </c>
       <c r="G98" t="n">
-        <v>58</v>
+        <v>338</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Гулько Эдуард Иванович</t>
+          <t>Гукун Галина Владимировна</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6395,16 +5615,16 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>46258</v>
+        <v>46035</v>
       </c>
       <c r="G99" t="n">
-        <v>51</v>
+        <v>274</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Васильева Анастасия Сергеевна</t>
+          <t xml:space="preserve">Бердибек кызы Альбина </t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6414,7 +5634,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6423,26 +5643,26 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>46258</v>
+        <v>46062</v>
       </c>
       <c r="G100" t="n">
-        <v>51</v>
+        <v>247</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Ефременко Альбина Вадимовна</t>
+          <t>Соколовский Ярослав</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6451,16 +5671,16 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>46265</v>
+        <v>46097</v>
       </c>
       <c r="G101" t="n">
-        <v>44</v>
+        <v>212</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Скрипкин Илья Павлович</t>
+          <t>Донец Дарья Константиновна</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6470,7 +5690,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6479,26 +5699,26 @@
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>46265</v>
+        <v>46133</v>
       </c>
       <c r="G102" t="n">
-        <v>44</v>
+        <v>176</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Фомина Анастасия Юрьевна</t>
+          <t>Ефремова Алина Олеговна</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6507,26 +5727,26 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>46280</v>
+        <v>46148</v>
       </c>
       <c r="G103" t="n">
-        <v>29</v>
+        <v>161</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ворсина Елизавета Евгеньевна</t>
+          <t>Уалива Альмира Эдуардовна</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6535,26 +5755,26 @@
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>46300</v>
+        <v>46170</v>
       </c>
       <c r="G104" t="n">
-        <v>9</v>
+        <v>139</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ковалева Виктория Сергеевна</t>
+          <t>Артамонова Валерия Олеговна</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6563,16 +5783,16 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>46290</v>
+        <v>46184</v>
       </c>
       <c r="G105" t="n">
-        <v>19</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Боброва Полина Сергеевна</t>
+          <t>Прокаева Виктория Сергеевна</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6591,21 +5811,21 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>46300</v>
+        <v>46189</v>
       </c>
       <c r="G106" t="n">
-        <v>9</v>
+        <v>120</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ким Полина Александровна</t>
+          <t>Кузьмин Матвей Игоревич</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6619,26 +5839,26 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>46307</v>
+        <v>46211</v>
       </c>
       <c r="G107" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лесничева Злата Александровна </t>
+          <t xml:space="preserve">Гайдук Анна Евгеньевна </t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Вечерний менеджер</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6647,26 +5867,26 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>46309</v>
+        <v>46203</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Каратаев Александр Владимирович</t>
+          <t>Фролов Евгений Аркадьевич</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Вечерний менеджер</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6675,37 +5895,541 @@
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>46309</v>
+        <v>46203</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Есиков Глеб Русланович </t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="G110" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Федоткина Наталья Евгеньевна</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="G111" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Наливайко Арсений Ильич</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G112" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Ибрагимова Анжелика Адалетовна</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G113" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Самарцев Захар Александрович </t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="G114" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Михеева Анна Сергеевна</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="G115" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Лазар Ярослава Витальевна</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="G116" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Гулько Эдуард Иванович</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="G117" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Васильева Анастасия Сергеевна</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="G118" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Ефременко Альбина Вадимовна</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G119" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Скрипкин Илья Павлович</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G120" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Фомина Анастасия Юрьевна</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="G121" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Ворсина Елизавета Евгеньевна</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G122" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Ковалева Виктория Сергеевна</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="G123" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Боброва Полина Сергеевна</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G124" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Ким Полина Александровна</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лесничева Злата Александровна </t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Каратаев Александр Владимирович</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
           <t>Ткачук Диана</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
         <is>
           <t>Вечерний менеджер</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>Работает</t>
         </is>
       </c>
-      <c r="E110" s="3" t="n">
+      <c r="E128" s="3" t="n">
         <v>46314</v>
       </c>
-      <c r="G110" t="n">
+      <c r="G128" t="n">
         <v>-5</v>
       </c>
     </row>

--- a/srok_raboty_bronirovanie_kontrol.xlsx
+++ b/srok_raboty_bronirovanie_kontrol.xlsx
@@ -258,12 +258,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Медиана для графика'!$A$2:$A$4</f>
+              <f>'Медиана для графика'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Медиана для графика'!$B$2:$B$4</f>
+              <f>'Медиана для графика'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -282,12 +282,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Медиана для графика'!$A$2:$A$4</f>
+              <f>'Медиана для графика'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Медиана для графика'!$C$2:$C$4</f>
+              <f>'Медиана для графика'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -306,12 +306,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Медиана для графика'!$A$2:$A$4</f>
+              <f>'Медиана для графика'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Медиана для графика'!$D$2:$D$4</f>
+              <f>'Медиана для графика'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -403,12 +403,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Количество для графика'!$A$2:$A$4</f>
+              <f>'Количество для графика'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Количество для графика'!$B$2:$B$4</f>
+              <f>'Количество для графика'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -427,12 +427,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Количество для графика'!$A$2:$A$4</f>
+              <f>'Количество для графика'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Количество для графика'!$C$2:$C$4</f>
+              <f>'Количество для графика'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -451,12 +451,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Количество для графика'!$A$2:$A$4</f>
+              <f>'Количество для графика'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Количество для графика'!$D$2:$D$4</f>
+              <f>'Количество для графика'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1053,7 +1053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1117,19 +1117,19 @@
         <v>2024</v>
       </c>
       <c r="D2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2" t="n">
+        <v>84</v>
+      </c>
+      <c r="F2" t="n">
+        <v>52</v>
+      </c>
+      <c r="G2" t="n">
         <v>11</v>
       </c>
-      <c r="E2" t="n">
-        <v>58</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
       <c r="H2" s="2" t="n">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="3">
@@ -1147,19 +1147,19 @@
         <v>2025</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="G3" t="n">
         <v>8</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="4">
@@ -1177,19 +1177,19 @@
         <v>2026</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>193</v>
+        <v>279</v>
       </c>
       <c r="F4" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="5">
@@ -1207,19 +1207,19 @@
         <v>2024</v>
       </c>
       <c r="D5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>157</v>
+      </c>
+      <c r="F5" t="n">
+        <v>111</v>
+      </c>
+      <c r="G5" t="n">
         <v>6</v>
       </c>
-      <c r="E5" t="n">
-        <v>54</v>
-      </c>
-      <c r="F5" t="n">
-        <v>38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
       <c r="H5" s="2" t="n">
-        <v>0.83</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="6">
@@ -1310,6 +1310,96 @@
       </c>
       <c r="H8" s="2" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Отдел контроля поездок</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>141</v>
+      </c>
+      <c r="F9" t="n">
+        <v>149</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Отдел контроля поездок</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>491</v>
+      </c>
+      <c r="F10" t="n">
+        <v>504</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Отдел контроля поездок</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>848</v>
+      </c>
+      <c r="F11" t="n">
+        <v>848</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1383,19 +1473,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>156</v>
+        <v>297</v>
       </c>
       <c r="E2" t="n">
-        <v>130</v>
+        <v>370</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="3">
@@ -1410,19 +1500,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="E3" t="n">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="4">
@@ -1437,19 +1527,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>247</v>
       </c>
       <c r="E4" t="n">
-        <v>130</v>
+        <v>267</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.33</v>
+        <v>0.16</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="5">
@@ -1464,19 +1554,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>256</v>
+        <v>369</v>
       </c>
       <c r="E5" t="n">
-        <v>188</v>
+        <v>273</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="6">
@@ -1491,19 +1581,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>179</v>
+        <v>256</v>
       </c>
       <c r="E6" t="n">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="7">
@@ -1518,19 +1608,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D7" t="n">
-        <v>210</v>
+        <v>305</v>
       </c>
       <c r="E7" t="n">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="8">
@@ -1545,19 +1635,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>227</v>
+        <v>287</v>
       </c>
       <c r="E8" t="n">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="9">
@@ -1572,19 +1662,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>352</v>
       </c>
       <c r="E9" t="n">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10">
@@ -1599,19 +1689,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D10" t="n">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="E10" t="n">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -1679,16 +1769,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>228</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3">
@@ -1701,16 +1791,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="F3" t="n">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4">
@@ -1723,16 +1813,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="F4" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5">
@@ -1878,7 +1968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1908,13 +1998,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="D2" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
@@ -1924,7 +2014,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="C3" t="n">
         <v>110</v>
@@ -1941,6 +2031,22 @@
       </c>
       <c r="D4" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Контроль: Отдел контроля поездок</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>149</v>
+      </c>
+      <c r="C5" t="n">
+        <v>504</v>
+      </c>
+      <c r="D5" t="n">
+        <v>848</v>
       </c>
     </row>
   </sheetData>
@@ -1955,7 +2061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1985,13 +2091,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -2001,7 +2107,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>20</v>
@@ -2024,6 +2130,22 @@
       </c>
       <c r="D4" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Контроль: Отдел контроля поездок</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2068,13 +2190,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="D2" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
@@ -2084,13 +2206,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="C3" t="n">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="D3" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2105,7 +2227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2172,13 +2294,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>850</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="4">
@@ -2193,13 +2315,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>424</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5">
@@ -2214,13 +2336,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>209</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6">
@@ -2231,38 +2353,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2026</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер 2/2</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2026</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
@@ -2273,17 +2395,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Вечерний менеджер</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>763</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -2298,13 +2420,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>426</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="10">
@@ -2319,13 +2441,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>186</v>
+        <v>763</v>
       </c>
     </row>
     <row r="11">
@@ -2336,17 +2458,80 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>Менеджер 2/2</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C13" t="n">
         <v>2026</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D13" t="n">
         <v>8</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E13" t="n">
         <v>31</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Отдел контроля поездок</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>926</v>
       </c>
     </row>
   </sheetData>
@@ -2360,7 +2545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2412,12 +2597,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дуйшенкул кызы Эрке</t>
+          <t>Ксения Коваленко</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2431,27 +2616,27 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>45315</v>
+        <v>44956</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>45350</v>
+        <v>44987</v>
       </c>
       <c r="G2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Морозова Кристина Александровна</t>
+          <t>Алтынай Шергазы Кызы</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2465,27 +2650,27 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>45426</v>
+        <v>44952</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>45436</v>
+        <v>45012</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ховалыг Дан-Хаяа Шолбановна</t>
+          <t>Пушкарева Лидия</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2499,22 +2684,22 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>45468</v>
+        <v>45012</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>45488</v>
+        <v>45015</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Удалова Виктория</t>
+          <t>Дружинина Наталья</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2533,27 +2718,27 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>45481</v>
+        <v>45012</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>45497</v>
+        <v>45030</v>
       </c>
       <c r="G5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Акимова Анастасия Константиновна</t>
+          <t>Нисофорова Анастасия</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2567,22 +2752,22 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>45474</v>
+        <v>45026</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>45526</v>
+        <v>45034</v>
       </c>
       <c r="G6" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Нахтигаль Глеб Сергеевич</t>
+          <t>Константин Афирдиев</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2601,27 +2786,27 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>45511</v>
+        <v>45131</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>45517</v>
+        <v>45187</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="H7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Коми Надежда Геннадьевна</t>
+          <t>Быстрова Маргарита</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2635,27 +2820,27 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>45488</v>
+        <v>45194</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>45560</v>
+        <v>45202</v>
       </c>
       <c r="G8" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Червинская Виктория</t>
+          <t>Беристова Алёна</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2669,27 +2854,27 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>45544</v>
+        <v>45145</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>45567</v>
+        <v>45215</v>
       </c>
       <c r="G9" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="H9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Карлин Иван</t>
+          <t>Карвандина Татьяна</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2703,22 +2888,22 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>45544</v>
+        <v>44951</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>45572</v>
+        <v>45169</v>
       </c>
       <c r="G10" t="n">
-        <v>28</v>
+        <v>218</v>
       </c>
       <c r="H10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Егембердиев Тимур</t>
+          <t>Королева Валерия</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2737,22 +2922,22 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>45575</v>
+        <v>45110</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>45583</v>
+        <v>45251</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="H11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Мухина Эльвира</t>
+          <t>Задорожный Александр</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2762,7 +2947,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2771,32 +2956,32 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>45509</v>
+        <v>45237</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>45586</v>
+        <v>45275</v>
       </c>
       <c r="G12" t="n">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="H12" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Козлова Мария Викторовна</t>
+          <t>Кислицын Даниил Дмитриевич</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2805,22 +2990,22 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>45474</v>
+        <v>45251</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>45610</v>
+        <v>45273</v>
       </c>
       <c r="G13" t="n">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="H13" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Беженарь Данил</t>
+          <t>Умуршадян Регина Александровна</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2830,7 +3015,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2839,22 +3024,22 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>45552</v>
+        <v>45254</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>45611</v>
+        <v>45271</v>
       </c>
       <c r="G14" t="n">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="H14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Гафуров Ильхом Азамджонович</t>
+          <t>Субботина Альбина</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2873,32 +3058,32 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>45482</v>
+        <v>45006</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>45628</v>
+        <v>45275</v>
       </c>
       <c r="G15" t="n">
-        <v>146</v>
+        <v>269</v>
       </c>
       <c r="H15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Минина Алена</t>
+          <t>Мельникова Элина</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2907,22 +3092,22 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>45628</v>
+        <v>45243</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>45638</v>
+        <v>45281</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H16" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Микрюков Олег </t>
+          <t>Вишнякова Ева</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2941,13 +3126,13 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>45495</v>
+        <v>44970</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>45652</v>
+        <v>45327</v>
       </c>
       <c r="G17" t="n">
-        <v>157</v>
+        <v>357</v>
       </c>
       <c r="H17" t="n">
         <v>2024</v>
@@ -2956,7 +3141,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Петрушина Александра</t>
+          <t>Коляко Виталий Олегович</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2975,13 +3160,13 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>45544</v>
+        <v>45281</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>45654</v>
+        <v>45327</v>
       </c>
       <c r="G18" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="H18" t="n">
         <v>2024</v>
@@ -2990,7 +3175,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Тильга Александра</t>
+          <t>Скачилов Максим Сергеевич</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3000,7 +3185,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3009,22 +3194,22 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>45623</v>
+        <v>45323</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>45699</v>
+        <v>45369</v>
       </c>
       <c r="G19" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="H19" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шостенко Артём </t>
+          <t>Дуйшенкул кызы Эрке</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3043,27 +3228,27 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>45671</v>
+        <v>45315</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>45705</v>
+        <v>45350</v>
       </c>
       <c r="G20" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H20" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Баздылев Иван</t>
+          <t>Назаров Максим Дмитриевич</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3077,22 +3262,22 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>45623</v>
+        <v>45383</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>45716</v>
+        <v>45384</v>
       </c>
       <c r="G21" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Лепехина Диана</t>
+          <t>Анисимов Иван</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3111,27 +3296,27 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>45531</v>
+        <v>44970</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>45734</v>
+        <v>45392</v>
       </c>
       <c r="G22" t="n">
-        <v>203</v>
+        <v>422</v>
       </c>
       <c r="H22" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Константинов Павел</t>
+          <t>Кривошеин Артур Эдуардович</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3145,32 +3330,32 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>45726</v>
+        <v>45308</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>45755</v>
+        <v>45404</v>
       </c>
       <c r="G23" t="n">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="H23" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Косицын Никита</t>
+          <t>Таранюк Лидия</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3179,22 +3364,22 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>45726</v>
+        <v>45261</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>45762</v>
+        <v>45418</v>
       </c>
       <c r="G24" t="n">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="H24" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Гребенщикова Софья</t>
+          <t>Байтыков Ринат</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3213,22 +3398,22 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>45650</v>
+        <v>45156</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>45789</v>
+        <v>45420</v>
       </c>
       <c r="G25" t="n">
-        <v>139</v>
+        <v>264</v>
       </c>
       <c r="H25" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Прожерина Кристина</t>
+          <t>Ивлев Фёдор Константинович</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3247,27 +3432,27 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>45735</v>
+        <v>45369</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>45799</v>
+        <v>45426</v>
       </c>
       <c r="G26" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H26" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цунаев Олег </t>
+          <t>Клеменкова Александра</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3281,22 +3466,22 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>45671</v>
+        <v>45399</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>45835</v>
+        <v>45400</v>
       </c>
       <c r="G27" t="n">
-        <v>164</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Березуцкая Светлана</t>
+          <t>Морозова Кристина Александровна</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3315,22 +3500,22 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>45454</v>
+        <v>45426</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>45842</v>
+        <v>45436</v>
       </c>
       <c r="G28" t="n">
-        <v>388</v>
+        <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Загнитковская Арина</t>
+          <t>Подлатов Михаил</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3340,7 +3525,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3349,32 +3534,32 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>45523</v>
+        <v>45440</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>45852</v>
+        <v>45449</v>
       </c>
       <c r="G29" t="n">
-        <v>329</v>
+        <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Тимофеев Никита Сергеевич</t>
+          <t>Живицкий Олег Вадимович</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3383,22 +3568,22 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>45834</v>
+        <v>45264</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>45847</v>
+        <v>45460</v>
       </c>
       <c r="G30" t="n">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="H30" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Степанов Тимофей</t>
+          <t>Колпаков Максим Станиславович</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3417,22 +3602,22 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>45749</v>
+        <v>45153</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>45854</v>
+        <v>45351</v>
       </c>
       <c r="G31" t="n">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="H31" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Герасименко Илья</t>
+          <t>Ильтимиров Никита Сергеевич</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3451,22 +3636,22 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>45810</v>
+        <v>45202</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>45854</v>
+        <v>45313</v>
       </c>
       <c r="G32" t="n">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="H32" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ткаченко Виктория</t>
+          <t>Малетин Андрей Сергеевич</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3476,7 +3661,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3485,32 +3670,32 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>45757</v>
+        <v>45308</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>45868</v>
+        <v>45457</v>
       </c>
       <c r="G33" t="n">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="H33" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Бельтяева Анель</t>
+          <t>Безденежных Владислав Альбертович</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3519,27 +3704,27 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>45811</v>
+        <v>45426</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>45870</v>
+        <v>45476</v>
       </c>
       <c r="G34" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H34" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Каминицкас Альгис Витальевич</t>
+          <t>Ховалыг Дан-Хаяа Шолбановна</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3553,22 +3738,22 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>45841</v>
+        <v>45468</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>45882</v>
+        <v>45488</v>
       </c>
       <c r="G35" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="H35" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Загнитковская Арина</t>
+          <t>Удалова Виктория</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3587,27 +3772,27 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>45523</v>
+        <v>45481</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>45852</v>
+        <v>45497</v>
       </c>
       <c r="G36" t="n">
-        <v>329</v>
+        <v>16</v>
       </c>
       <c r="H36" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Кашулин Данил Сергеевич</t>
+          <t>Дробина Анастасия Денисовна</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3621,22 +3806,22 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>45887</v>
+        <v>45237</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>45891</v>
+        <v>45534</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>297</v>
       </c>
       <c r="H37" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Корчикова Дарья Евгеньевна </t>
+          <t>Денк Данила Андреевич</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3655,32 +3840,32 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>45831</v>
+        <v>45251</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>45901</v>
+        <v>45534</v>
       </c>
       <c r="G38" t="n">
-        <v>70</v>
+        <v>283</v>
       </c>
       <c r="H38" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Новокшанов Егор Леонидович</t>
+          <t>Подлипаева Екатерина Андреевна</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3689,22 +3874,22 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>45712</v>
+        <v>45261</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>45901</v>
+        <v>45527</v>
       </c>
       <c r="G39" t="n">
-        <v>189</v>
+        <v>266</v>
       </c>
       <c r="H39" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Тыщенко Анжелика Сергеевна</t>
+          <t>Дьяконов Андрей Андреевич</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3714,7 +3899,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3723,22 +3908,22 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>45481</v>
+        <v>45261</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>45904</v>
+        <v>45526</v>
       </c>
       <c r="G40" t="n">
-        <v>423</v>
+        <v>265</v>
       </c>
       <c r="H40" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Кирнос Наталья</t>
+          <t>Акимова Анастасия Константиновна</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3757,27 +3942,27 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>45544</v>
+        <v>45474</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>45904</v>
+        <v>45526</v>
       </c>
       <c r="G41" t="n">
-        <v>360</v>
+        <v>52</v>
       </c>
       <c r="H41" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Новокшанов Егор Леонидович</t>
+          <t>Нахтигаль Глеб Сергеевич</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3791,22 +3976,22 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>45712</v>
+        <v>45511</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>45901</v>
+        <v>45517</v>
       </c>
       <c r="G42" t="n">
-        <v>189</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Винтер Максим Генрихович</t>
+          <t>Остапчук Олеся Дмитриевна</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3825,27 +4010,27 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>45775</v>
+        <v>45176</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>45922</v>
+        <v>45539</v>
       </c>
       <c r="G43" t="n">
-        <v>147</v>
+        <v>363</v>
       </c>
       <c r="H43" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Торден Дамиан </t>
+          <t>Коми Надежда Геннадьевна</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3859,27 +4044,27 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>45819</v>
+        <v>45488</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>45929</v>
+        <v>45560</v>
       </c>
       <c r="G44" t="n">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="H44" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Винтер Максим Генрихович</t>
+          <t>Червинская Виктория</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3893,22 +4078,22 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>45775</v>
+        <v>45544</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>45922</v>
+        <v>45567</v>
       </c>
       <c r="G45" t="n">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="H45" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Данькова Анастасия Сергеевна</t>
+          <t>Карлин Иван</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3927,22 +4112,22 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>45894</v>
+        <v>45544</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>45951</v>
+        <v>45572</v>
       </c>
       <c r="G46" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="H46" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Бураков Григорий Радиевич</t>
+          <t>Егембердиев Тимур</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3961,22 +4146,22 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>45772</v>
+        <v>45575</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>45957</v>
+        <v>45583</v>
       </c>
       <c r="G47" t="n">
-        <v>185</v>
+        <v>8</v>
       </c>
       <c r="H47" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Парфенова Анастасия Игоревна</t>
+          <t>Мухина Эльвира</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3995,22 +4180,22 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>45916</v>
+        <v>45509</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>45968</v>
+        <v>45586</v>
       </c>
       <c r="G48" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="H48" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Монгуш Анай-Хаак Андреевна</t>
+          <t>Азаренко Александра Юрьевна</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4020,7 +4205,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4029,22 +4214,22 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>45950</v>
+        <v>45467</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>46001</v>
+        <v>45598</v>
       </c>
       <c r="G49" t="n">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="H49" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Смирнова Полина Ильинична</t>
+          <t>Козлова Мария Викторовна</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4063,22 +4248,22 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>45958</v>
+        <v>45474</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>46017</v>
+        <v>45610</v>
       </c>
       <c r="G50" t="n">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="H50" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Федоринова София Владимировна</t>
+          <t>Беженарь Данил</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4097,27 +4282,27 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>45908</v>
+        <v>45552</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>46021</v>
+        <v>45611</v>
       </c>
       <c r="G51" t="n">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="H51" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Креймер Константин Андреевич</t>
+          <t>Гафуров Ильхом Азамджонович</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4131,27 +4316,27 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>45944</v>
+        <v>45482</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>46038</v>
+        <v>45628</v>
       </c>
       <c r="G52" t="n">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="H52" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Телков Данил Артемович</t>
+          <t>Минина Алена</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4165,22 +4350,22 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>45791</v>
+        <v>45628</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>46045</v>
+        <v>45638</v>
       </c>
       <c r="G53" t="n">
-        <v>254</v>
+        <v>10</v>
       </c>
       <c r="H53" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Доржу Долума Шой-ооловна</t>
+          <t xml:space="preserve">Микрюков Олег </t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4199,27 +4384,27 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>45880</v>
+        <v>45495</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>46059</v>
+        <v>45652</v>
       </c>
       <c r="G54" t="n">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="H54" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Лаврентьева Ульяна Ивановна</t>
+          <t>Петрушина Александра</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4233,27 +4418,27 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>46036</v>
+        <v>45544</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>46083</v>
+        <v>45654</v>
       </c>
       <c r="G55" t="n">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="H55" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Рыбников Бронислав Игоревич</t>
+          <t>Тильга Александра</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4267,27 +4452,27 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>46038</v>
+        <v>45623</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>46080</v>
+        <v>45699</v>
       </c>
       <c r="G56" t="n">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="H56" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Домрачев Иван Дмитриевич</t>
+          <t xml:space="preserve">Шостенко Артём </t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4301,22 +4486,22 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>46091</v>
+        <v>45671</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>46097</v>
+        <v>45705</v>
       </c>
       <c r="G57" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H57" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Хрипченко Анастасия Олеговна</t>
+          <t>Баздылев Иван</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4335,27 +4520,27 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>45971</v>
+        <v>45623</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>46099</v>
+        <v>45716</v>
       </c>
       <c r="G58" t="n">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="H58" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Кириченко Ангелина Вячеславовна</t>
+          <t>Лепехина Диана</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4369,22 +4554,22 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>45771</v>
+        <v>45531</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>46104</v>
+        <v>45734</v>
       </c>
       <c r="G59" t="n">
-        <v>333</v>
+        <v>203</v>
       </c>
       <c r="H59" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шивлякова Мария </t>
+          <t>Константинов Павел</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4403,27 +4588,27 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>46128</v>
+        <v>45726</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>46133</v>
+        <v>45755</v>
       </c>
       <c r="G60" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H60" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Савкин Глеб Петрович </t>
+          <t>Косицын Никита</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4437,27 +4622,27 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>45939</v>
+        <v>45726</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>46141</v>
+        <v>45762</v>
       </c>
       <c r="G61" t="n">
-        <v>202</v>
+        <v>36</v>
       </c>
       <c r="H61" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ковалева Виктория Сергеевна</t>
+          <t>Нуянзина Мила Андреевна</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4471,32 +4656,32 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>45945</v>
+        <v>45272</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>46140</v>
+        <v>45777</v>
       </c>
       <c r="G62" t="n">
-        <v>195</v>
+        <v>505</v>
       </c>
       <c r="H62" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Монгуш Тензин</t>
+          <t>Бекреев Михаил Михайлович</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4505,22 +4690,22 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>45589</v>
+        <v>45279</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>46142</v>
+        <v>45782</v>
       </c>
       <c r="G63" t="n">
-        <v>553</v>
+        <v>503</v>
       </c>
       <c r="H63" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чернятьева Рина Витальевна </t>
+          <t>Федотов Александр</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4530,7 +4715,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4539,27 +4724,27 @@
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>46077</v>
+        <v>45408</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>46146</v>
+        <v>45782</v>
       </c>
       <c r="G64" t="n">
-        <v>69</v>
+        <v>374</v>
       </c>
       <c r="H64" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Карпова Валерия константиновна</t>
+          <t>Гребенщикова Софья</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4573,32 +4758,32 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>45890</v>
+        <v>45650</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>46147</v>
+        <v>45789</v>
       </c>
       <c r="G65" t="n">
-        <v>257</v>
+        <v>139</v>
       </c>
       <c r="H65" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Кладов Антон Павлович</t>
+          <t>Глуховская (Мамонтова) Анна Дмитриевна</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4607,22 +4792,22 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>46133</v>
+        <v>45280</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>46161</v>
+        <v>45784</v>
       </c>
       <c r="G66" t="n">
-        <v>28</v>
+        <v>504</v>
       </c>
       <c r="H66" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Черкасова Полина</t>
+          <t>Прожерина Кристина</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4641,22 +4826,22 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>45749</v>
+        <v>45735</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>46171</v>
+        <v>45799</v>
       </c>
       <c r="G67" t="n">
-        <v>422</v>
+        <v>64</v>
       </c>
       <c r="H67" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Резинкина Анастасия</t>
+          <t>Немчинов Михаил</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4675,22 +4860,22 @@
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>46162</v>
+        <v>45237</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>46183</v>
+        <v>45807</v>
       </c>
       <c r="G68" t="n">
-        <v>21</v>
+        <v>570</v>
       </c>
       <c r="H68" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чудинова Полина Владимировна  </t>
+          <t xml:space="preserve">Цунаев Олег </t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4709,22 +4894,22 @@
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>45880</v>
+        <v>45671</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>46178</v>
+        <v>45835</v>
       </c>
       <c r="G69" t="n">
-        <v>298</v>
+        <v>164</v>
       </c>
       <c r="H69" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Самодурова Арина</t>
+          <t>Березуцкая Светлана</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4743,27 +4928,27 @@
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>46164</v>
+        <v>45454</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>46188</v>
+        <v>45842</v>
       </c>
       <c r="G70" t="n">
-        <v>24</v>
+        <v>388</v>
       </c>
       <c r="H70" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Сыдыбаев Жалынбек Сыртбаевич</t>
+          <t>Загнитковская Арина</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4777,27 +4962,27 @@
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>46181</v>
+        <v>45523</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>46189</v>
+        <v>45852</v>
       </c>
       <c r="G71" t="n">
-        <v>8</v>
+        <v>329</v>
       </c>
       <c r="H71" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Мищенко Михаил Витальевич</t>
+          <t>Тимофеев Никита Сергеевич</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4811,27 +4996,27 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>45966</v>
+        <v>45834</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>46220</v>
+        <v>45847</v>
       </c>
       <c r="G72" t="n">
-        <v>254</v>
+        <v>13</v>
       </c>
       <c r="H72" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Долгополова Елена Сергеевна</t>
+          <t>Степанов Тимофей</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4845,27 +5030,27 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>46174</v>
+        <v>45749</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>46223</v>
+        <v>45854</v>
       </c>
       <c r="G73" t="n">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="H73" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Жигалёв Денис Евгеньевич</t>
+          <t>Герасименко Илья</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4879,27 +5064,27 @@
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>46203</v>
+        <v>45810</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>46227</v>
+        <v>45854</v>
       </c>
       <c r="G74" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="H74" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Кочева Анна Алексеевна</t>
+          <t>Ткаченко Виктория</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4913,22 +5098,22 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>46062</v>
+        <v>45757</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>46227</v>
+        <v>45868</v>
       </c>
       <c r="G75" t="n">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="H75" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Гундарева Виктория Константиновна</t>
+          <t>Бельтяева Анель</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4947,22 +5132,22 @@
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>46085</v>
+        <v>45811</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>46234</v>
+        <v>45870</v>
       </c>
       <c r="G76" t="n">
-        <v>149</v>
+        <v>59</v>
       </c>
       <c r="H76" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Сериккали Мадина</t>
+          <t>Каминицкас Альгис Витальевич</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4972,7 +5157,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4981,32 +5166,32 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>46237</v>
+        <v>45841</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>46252</v>
+        <v>45882</v>
       </c>
       <c r="G77" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H77" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Власов Тимофей Антонович</t>
+          <t>Немчинов Михаил</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5015,32 +5200,32 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>46258</v>
+        <v>45237</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>46266</v>
+        <v>45807</v>
       </c>
       <c r="G78" t="n">
-        <v>8</v>
+        <v>570</v>
       </c>
       <c r="H78" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Троельникова Софья</t>
+          <t>Глуховская (Мамонтова) Анна Дмитриевна</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5049,22 +5234,22 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>45733</v>
+        <v>45280</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>46251</v>
+        <v>45784</v>
       </c>
       <c r="G79" t="n">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="H79" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Сазонов Сергей Викторович</t>
+          <t>Нуянзина Мила Андреевна</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5079,20 +5264,26 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>45390</v>
+        <v>45272</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>45777</v>
       </c>
       <c r="G80" t="n">
-        <v>919</v>
+        <v>505</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кралинова Алена Алексеевна </t>
+          <t>Загнитковская Арина</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5107,20 +5298,26 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>45502</v>
+        <v>45523</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>45852</v>
       </c>
       <c r="G81" t="n">
-        <v>807</v>
+        <v>329</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Русских Юлия</t>
+          <t>Кашулин Данил Сергеевич</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5135,20 +5332,26 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>45520</v>
+        <v>45887</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>45891</v>
       </c>
       <c r="G82" t="n">
-        <v>789</v>
+        <v>4</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Светашова Анастасия Владимировна</t>
+          <t xml:space="preserve">Корчикова Дарья Евгеньевна </t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5163,25 +5366,31 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>45527</v>
+        <v>45831</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>45901</v>
       </c>
       <c r="G83" t="n">
-        <v>782</v>
+        <v>70</v>
+      </c>
+      <c r="H83" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Шакирзянова Куддусия</t>
+          <t>Новокшанов Егор Леонидович</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5191,20 +5400,26 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>45616</v>
+        <v>45712</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>45901</v>
       </c>
       <c r="G84" t="n">
-        <v>693</v>
+        <v>189</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Краснов Сергей Витальевич</t>
+          <t>Тыщенко Анжелика Сергеевна</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5219,25 +5434,31 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>45775</v>
+        <v>45481</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>45904</v>
       </c>
       <c r="G85" t="n">
-        <v>534</v>
+        <v>423</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лемешев Филипп Игоревич </t>
+          <t>Кирнос Наталья</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5247,20 +5468,26 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>45792</v>
+        <v>45544</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>45904</v>
       </c>
       <c r="G86" t="n">
-        <v>517</v>
+        <v>360</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Польховская Анастасия Алексеевна</t>
+          <t>Новокшанов Егор Леонидович</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5275,25 +5502,31 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>45834</v>
+        <v>45712</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>45901</v>
       </c>
       <c r="G87" t="n">
-        <v>475</v>
+        <v>189</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Яруткина Александра Константиновна </t>
+          <t>Винтер Максим Генрихович</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5303,20 +5536,26 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>45839</v>
+        <v>45775</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>45922</v>
       </c>
       <c r="G88" t="n">
-        <v>470</v>
+        <v>147</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Голев Кирилл Андреевич</t>
+          <t>Приходько Илья Олегович</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5326,25 +5565,31 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Менеджер (основной)</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>45845</v>
+        <v>45351</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>45923</v>
       </c>
       <c r="G89" t="n">
-        <v>464</v>
+        <v>572</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Сакирко Виктория Алексеевна</t>
+          <t xml:space="preserve">Торден Дамиан </t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5359,25 +5604,31 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>45838</v>
+        <v>45819</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>45929</v>
       </c>
       <c r="G90" t="n">
-        <v>471</v>
+        <v>110</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Лебёдка Богдан Константинович</t>
+          <t>Винтер Максим Генрихович</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5387,25 +5638,31 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>45890</v>
+        <v>45775</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>45922</v>
       </c>
       <c r="G91" t="n">
-        <v>419</v>
+        <v>147</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Габазов Тимур Алиханович</t>
+          <t>Данькова Анастасия Сергеевна</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5415,25 +5672,31 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>45880</v>
+        <v>45894</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>45951</v>
       </c>
       <c r="G92" t="n">
-        <v>429</v>
+        <v>57</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Бобров Андрей Юрьевич</t>
+          <t>Бураков Григорий Радиевич</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5443,25 +5706,31 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>45930</v>
+        <v>45772</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>45957</v>
       </c>
       <c r="G93" t="n">
-        <v>379</v>
+        <v>185</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Матющенко Ксения Евгеньевна</t>
+          <t>Парфенова Анастасия Игоревна</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5471,20 +5740,26 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>45930</v>
+        <v>45916</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>45968</v>
       </c>
       <c r="G94" t="n">
-        <v>379</v>
+        <v>52</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Бахтина Виктория Александровна</t>
+          <t>Монгуш Анай-Хаак Андреевна</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5499,25 +5774,31 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>45944</v>
+        <v>45950</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>46001</v>
       </c>
       <c r="G95" t="n">
-        <v>365</v>
+        <v>51</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Коркунова Дарья Витальевна</t>
+          <t>Смирнова Полина Ильинична</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5527,20 +5808,26 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
         <v>45958</v>
       </c>
+      <c r="F96" s="3" t="n">
+        <v>46017</v>
+      </c>
       <c r="G96" t="n">
-        <v>351</v>
+        <v>59</v>
+      </c>
+      <c r="H96" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Московских Алёна Владимировна</t>
+          <t>Федоринова София Владимировна</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5555,20 +5842,26 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>45945</v>
+        <v>45908</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>46021</v>
       </c>
       <c r="G97" t="n">
-        <v>364</v>
+        <v>113</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Петрова Евгения Вячеславовна</t>
+          <t>Креймер Константин Андреевич</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5583,25 +5876,31 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>45971</v>
+        <v>45944</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>46038</v>
       </c>
       <c r="G98" t="n">
-        <v>338</v>
+        <v>94</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Гукун Галина Владимировна</t>
+          <t>Телков Данил Артемович</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5611,25 +5910,31 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>46035</v>
+        <v>45791</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>46045</v>
       </c>
       <c r="G99" t="n">
-        <v>274</v>
+        <v>254</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бердибек кызы Альбина </t>
+          <t>Доржу Долума Шой-ооловна</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5639,20 +5944,26 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>46062</v>
+        <v>45880</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>46059</v>
       </c>
       <c r="G100" t="n">
-        <v>247</v>
+        <v>179</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Соколовский Ярослав</t>
+          <t>Лаврентьева Ульяна Ивановна</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5667,20 +5978,26 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>46097</v>
+        <v>46036</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>46083</v>
       </c>
       <c r="G101" t="n">
-        <v>212</v>
+        <v>47</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Донец Дарья Константиновна</t>
+          <t>Рыбников Бронислав Игоревич</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5695,20 +6012,26 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>46133</v>
+        <v>46038</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>46080</v>
       </c>
       <c r="G102" t="n">
-        <v>176</v>
+        <v>42</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ефремова Алина Олеговна</t>
+          <t>Домрачев Иван Дмитриевич</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5723,25 +6046,31 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>46148</v>
+        <v>46091</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>46097</v>
       </c>
       <c r="G103" t="n">
-        <v>161</v>
+        <v>6</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Уалива Альмира Эдуардовна</t>
+          <t>Хрипченко Анастасия Олеговна</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5751,20 +6080,26 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>46170</v>
+        <v>45971</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="G104" t="n">
-        <v>139</v>
+        <v>128</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Артамонова Валерия Олеговна</t>
+          <t>Кириченко Ангелина Вячеславовна</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5774,25 +6109,31 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>46184</v>
+        <v>45771</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>46104</v>
       </c>
       <c r="G105" t="n">
-        <v>125</v>
+        <v>333</v>
+      </c>
+      <c r="H105" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Прокаева Виктория Сергеевна</t>
+          <t>Ерыгин Евгений Игоревич</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5802,109 +6143,133 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Отдел контроля поездок</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>46189</v>
+        <v>45264</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>46112</v>
       </c>
       <c r="G106" t="n">
-        <v>120</v>
+        <v>848</v>
+      </c>
+      <c r="H106" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Кузьмин Матвей Игоревич</t>
+          <t xml:space="preserve">Шивлякова Мария </t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>46211</v>
+        <v>46128</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>46133</v>
       </c>
       <c r="G107" t="n">
-        <v>98</v>
+        <v>5</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Гайдук Анна Евгеньевна </t>
+          <t xml:space="preserve">Савкин Глеб Петрович </t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>46203</v>
+        <v>45939</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>46141</v>
       </c>
       <c r="G108" t="n">
-        <v>106</v>
+        <v>202</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Фролов Евгений Аркадьевич</t>
+          <t>Ковалева Виктория Сергеевна</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>46203</v>
+        <v>45945</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>46140</v>
       </c>
       <c r="G109" t="n">
-        <v>106</v>
+        <v>195</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Есиков Глеб Русланович </t>
+          <t>Монгуш Тензин</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5914,53 +6279,65 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>46216</v>
+        <v>45589</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>46142</v>
       </c>
       <c r="G110" t="n">
-        <v>93</v>
+        <v>553</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Федоткина Наталья Евгеньевна</t>
+          <t xml:space="preserve">Чернятьева Рина Витальевна </t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>46223</v>
+        <v>46077</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>46146</v>
       </c>
       <c r="G111" t="n">
-        <v>86</v>
+        <v>69</v>
+      </c>
+      <c r="H111" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Наливайко Арсений Ильич</t>
+          <t>Карпова Валерия константиновна</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5970,25 +6347,31 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>46244</v>
+        <v>45890</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>46147</v>
       </c>
       <c r="G112" t="n">
-        <v>65</v>
+        <v>257</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Ибрагимова Анжелика Адалетовна</t>
+          <t>Кладов Антон Павлович</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5998,25 +6381,31 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>46244</v>
+        <v>46133</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>46161</v>
       </c>
       <c r="G113" t="n">
-        <v>65</v>
+        <v>28</v>
+      </c>
+      <c r="H113" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Самарцев Захар Александрович </t>
+          <t>Черкасова Полина</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6026,25 +6415,31 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>46251</v>
+        <v>45749</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>46171</v>
       </c>
       <c r="G114" t="n">
-        <v>58</v>
+        <v>422</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Михеева Анна Сергеевна</t>
+          <t>Резинкина Анастасия</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6054,81 +6449,99 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>46253</v>
+        <v>46162</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>46183</v>
       </c>
       <c r="G115" t="n">
-        <v>56</v>
+        <v>21</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Лазар Ярослава Витальевна</t>
+          <t>Рожнева Елизавета</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>46251</v>
+        <v>45272</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>46181</v>
       </c>
       <c r="G116" t="n">
-        <v>58</v>
+        <v>909</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Гулько Эдуард Иванович</t>
+          <t xml:space="preserve">Чудинова Полина Владимировна  </t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>46258</v>
+        <v>45880</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>46178</v>
       </c>
       <c r="G117" t="n">
-        <v>51</v>
+        <v>298</v>
+      </c>
+      <c r="H117" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Васильева Анастасия Сергеевна</t>
+          <t>Самодурова Арина</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6138,25 +6551,31 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>46258</v>
+        <v>46164</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>46188</v>
       </c>
       <c r="G118" t="n">
-        <v>51</v>
+        <v>24</v>
+      </c>
+      <c r="H118" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ефременко Альбина Вадимовна</t>
+          <t>Сыдыбаев Жалынбек Сыртбаевич</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6166,53 +6585,65 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>46265</v>
+        <v>46181</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>46189</v>
       </c>
       <c r="G119" t="n">
-        <v>44</v>
+        <v>8</v>
+      </c>
+      <c r="H119" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Скрипкин Илья Павлович</t>
+          <t>Мищенко Михаил Витальевич</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Бронирование</t>
+          <t>Контроль</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>46265</v>
+        <v>45966</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>46220</v>
       </c>
       <c r="G120" t="n">
-        <v>44</v>
+        <v>254</v>
+      </c>
+      <c r="H120" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Фомина Анастасия Юрьевна</t>
+          <t>Долгополова Елена Сергеевна</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6222,109 +6653,133 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>46280</v>
+        <v>46174</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>46223</v>
       </c>
       <c r="G121" t="n">
-        <v>29</v>
+        <v>49</v>
+      </c>
+      <c r="H121" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ворсина Елизавета Евгеньевна</t>
+          <t>Жигалёв Денис Евгеньевич</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E122" s="3" t="n">
-        <v>46300</v>
+        <v>46203</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>46227</v>
       </c>
       <c r="G122" t="n">
-        <v>9</v>
+        <v>24</v>
+      </c>
+      <c r="H122" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ковалева Виктория Сергеевна</t>
+          <t>Кочева Анна Алексеевна</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Вечерний менеджер</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>46290</v>
+        <v>46062</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>46227</v>
       </c>
       <c r="G123" t="n">
-        <v>19</v>
+        <v>165</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Боброва Полина Сергеевна</t>
+          <t>Гундарева Виктория Константиновна</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>46300</v>
+        <v>46085</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>46234</v>
       </c>
       <c r="G124" t="n">
-        <v>9</v>
+        <v>149</v>
+      </c>
+      <c r="H124" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ким Полина Александровна</t>
+          <t>Сериккали Мадина</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6339,20 +6794,26 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>46307</v>
+        <v>46237</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>46252</v>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лесничева Злата Александровна </t>
+          <t>Власов Тимофей Антонович</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6367,69 +6828,1571 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>46309</v>
+        <v>46258</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>46266</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Каратаев Александр Владимирович</t>
+          <t>Троельникова Софья</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Бронирование</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Менеджер 2/2</t>
+          <t>Менеджер (основной)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Работает</t>
+          <t>Уволен</t>
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>46309</v>
+        <v>45733</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>46251</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>518</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>Решетень Регина Федоровна</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Уволен</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>45329</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>46272</v>
+      </c>
+      <c r="G128" t="n">
+        <v>943</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Рябик Арина Александровна</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>45194</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Никитюк Леон</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>45287</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Берлин Аександра</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>45268</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Кузьменко Александра Константиновна</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Отдел контроля поездок</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>45383</v>
+      </c>
+      <c r="G132" t="n">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Сазонов Сергей Викторович</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>45390</v>
+      </c>
+      <c r="G133" t="n">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кралинова Алена Алексеевна </t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>45502</v>
+      </c>
+      <c r="G134" t="n">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Русских Юлия</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>45520</v>
+      </c>
+      <c r="G135" t="n">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Светашова Анастасия Владимировна</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>45527</v>
+      </c>
+      <c r="G136" t="n">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Шакирзянова Куддусия</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>45616</v>
+      </c>
+      <c r="G137" t="n">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Краснов Сергей Витальевич</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>45775</v>
+      </c>
+      <c r="G138" t="n">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лемешев Филипп Игоревич </t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>45792</v>
+      </c>
+      <c r="G139" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Польховская Анастасия Алексеевна</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="G140" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Яруткина Александра Константиновна </t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>45839</v>
+      </c>
+      <c r="G141" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Голев Кирилл Андреевич</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>45845</v>
+      </c>
+      <c r="G142" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Сакирко Виктория Алексеевна</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>45838</v>
+      </c>
+      <c r="G143" t="n">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Лебёдка Богдан Константинович</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>45890</v>
+      </c>
+      <c r="G144" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Габазов Тимур Алиханович</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>45880</v>
+      </c>
+      <c r="G145" t="n">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Бобров Андрей Юрьевич</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="G146" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Матющенко Ксения Евгеньевна</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="G147" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Бахтина Виктория Александровна</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>45944</v>
+      </c>
+      <c r="G148" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Коркунова Дарья Витальевна</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="G149" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Московских Алёна Владимировна</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>45945</v>
+      </c>
+      <c r="G150" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Петрова Евгения Вячеславовна</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>45971</v>
+      </c>
+      <c r="G151" t="n">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Гукун Галина Владимировна</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="G152" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Бердибек кызы Альбина </t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>46062</v>
+      </c>
+      <c r="G153" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Соколовский Ярослав</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>46097</v>
+      </c>
+      <c r="G154" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Донец Дарья Константиновна</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>46133</v>
+      </c>
+      <c r="G155" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Ефремова Алина Олеговна</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>46148</v>
+      </c>
+      <c r="G156" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Уалива Альмира Эдуардовна</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Менеджер (основной)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>46170</v>
+      </c>
+      <c r="G157" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Артамонова Валерия Олеговна</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>46184</v>
+      </c>
+      <c r="G158" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Прокаева Виктория Сергеевна</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>46189</v>
+      </c>
+      <c r="G159" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Кузьмин Матвей Игоревич</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>46211</v>
+      </c>
+      <c r="G160" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Гайдук Анна Евгеньевна </t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="G161" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Фролов Евгений Аркадьевич</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="G162" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Есиков Глеб Русланович </t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="G163" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Федоткина Наталья Евгеньевна</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="G164" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Наливайко Арсений Ильич</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G165" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Ибрагимова Анжелика Адалетовна</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G166" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Самарцев Захар Александрович </t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="G167" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Михеева Анна Сергеевна</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="G168" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Лазар Ярослава Витальевна</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="G169" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Гулько Эдуард Иванович</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="G170" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Васильева Анастасия Сергеевна</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="G171" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Ефременко Альбина Вадимовна</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G172" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Скрипкин Илья Павлович</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G173" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Фомина Анастасия Юрьевна</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="G174" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Ворсина Елизавета Евгеньевна</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G175" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Ковалева Виктория Сергеевна</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Вечерний менеджер</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="G176" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Боброва Полина Сергеевна</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G177" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Ким Полина Александровна</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G178" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лесничева Злата Александровна </t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Каратаев Александр Владимирович</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Менеджер 2/2</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Работает</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
           <t>Ткачук Диана</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Бронирование</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Бронирование</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
         <is>
           <t>Вечерний менеджер</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>Работает</t>
         </is>
       </c>
-      <c r="E128" s="3" t="n">
+      <c r="E181" s="3" t="n">
         <v>46314</v>
       </c>
-      <c r="G128" t="n">
+      <c r="G181" t="n">
         <v>-5</v>
       </c>
     </row>
